--- a/thaco/color/Viet/1_Office_color_Viet.xlsx
+++ b/thaco/color/Viet/1_Office_color_Viet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/Viet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B8B68A-A03B-0C41-8AB3-423BEA8F1F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2526F47-BB80-1E46-945F-6179AFC3C54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38560" yWindow="660" windowWidth="38100" windowHeight="20800" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -4545,7 +4545,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="239">
   <si>
     <t>COMPANY …..............</t>
   </si>
@@ -5276,6 +5276,9 @@
   </si>
   <si>
     <t>Các khoản được hưởng</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -6984,6 +6987,93 @@
     <xf numFmtId="164" fontId="29" fillId="8" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="70" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="70" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="70" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6993,13 +7083,109 @@
     <xf numFmtId="165" fontId="8" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7011,15 +7197,6 @@
     <xf numFmtId="164" fontId="22" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7035,220 +7212,54 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="70" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="70" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="70" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="3" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -7257,10 +7268,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7268,131 +7279,123 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8193,88 +8196,88 @@
       <c r="CD2" s="293"/>
     </row>
     <row r="3" spans="1:87" s="14" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="391"/>
-      <c r="B3" s="389"/>
-      <c r="C3" s="389"/>
-      <c r="D3" s="389"/>
-      <c r="E3" s="389"/>
-      <c r="F3" s="389"/>
-      <c r="G3" s="389"/>
-      <c r="H3" s="389"/>
-      <c r="I3" s="389"/>
-      <c r="J3" s="389"/>
-      <c r="K3" s="389"/>
-      <c r="L3" s="389"/>
-      <c r="M3" s="389"/>
-      <c r="N3" s="389"/>
-      <c r="O3" s="389"/>
-      <c r="P3" s="389"/>
-      <c r="Q3" s="389"/>
-      <c r="R3" s="389"/>
-      <c r="S3" s="389"/>
-      <c r="T3" s="389"/>
-      <c r="U3" s="389"/>
-      <c r="V3" s="389"/>
-      <c r="W3" s="389"/>
-      <c r="X3" s="389"/>
-      <c r="Y3" s="389"/>
-      <c r="Z3" s="389"/>
-      <c r="AA3" s="389"/>
-      <c r="AB3" s="389"/>
-      <c r="AC3" s="389"/>
-      <c r="AD3" s="389"/>
-      <c r="AE3" s="389"/>
-      <c r="AF3" s="389"/>
-      <c r="AG3" s="389"/>
-      <c r="AH3" s="389"/>
-      <c r="AI3" s="389"/>
-      <c r="AJ3" s="389"/>
-      <c r="AK3" s="389"/>
-      <c r="AL3" s="389"/>
-      <c r="AM3" s="389"/>
-      <c r="AN3" s="389"/>
-      <c r="AO3" s="389"/>
-      <c r="AP3" s="389"/>
-      <c r="AQ3" s="389"/>
-      <c r="AR3" s="389"/>
-      <c r="AS3" s="389"/>
-      <c r="AT3" s="389"/>
-      <c r="AU3" s="389"/>
-      <c r="AV3" s="389"/>
-      <c r="AW3" s="389"/>
-      <c r="AX3" s="389"/>
-      <c r="AY3" s="389"/>
-      <c r="AZ3" s="389"/>
-      <c r="BA3" s="389"/>
-      <c r="BB3" s="389"/>
-      <c r="BC3" s="389"/>
-      <c r="BD3" s="389"/>
-      <c r="BE3" s="389"/>
-      <c r="BF3" s="389"/>
-      <c r="BG3" s="389"/>
-      <c r="BH3" s="389"/>
-      <c r="BI3" s="389"/>
-      <c r="BJ3" s="389"/>
-      <c r="BK3" s="389"/>
-      <c r="BL3" s="389"/>
-      <c r="BM3" s="389"/>
-      <c r="BN3" s="389"/>
-      <c r="BO3" s="389"/>
-      <c r="BP3" s="389"/>
-      <c r="BQ3" s="389"/>
-      <c r="BR3" s="389"/>
-      <c r="BS3" s="389"/>
-      <c r="BT3" s="389"/>
-      <c r="BU3" s="389"/>
+      <c r="A3" s="368"/>
+      <c r="B3" s="361"/>
+      <c r="C3" s="361"/>
+      <c r="D3" s="361"/>
+      <c r="E3" s="361"/>
+      <c r="F3" s="361"/>
+      <c r="G3" s="361"/>
+      <c r="H3" s="361"/>
+      <c r="I3" s="361"/>
+      <c r="J3" s="361"/>
+      <c r="K3" s="361"/>
+      <c r="L3" s="361"/>
+      <c r="M3" s="361"/>
+      <c r="N3" s="361"/>
+      <c r="O3" s="361"/>
+      <c r="P3" s="361"/>
+      <c r="Q3" s="361"/>
+      <c r="R3" s="361"/>
+      <c r="S3" s="361"/>
+      <c r="T3" s="361"/>
+      <c r="U3" s="361"/>
+      <c r="V3" s="361"/>
+      <c r="W3" s="361"/>
+      <c r="X3" s="361"/>
+      <c r="Y3" s="361"/>
+      <c r="Z3" s="361"/>
+      <c r="AA3" s="361"/>
+      <c r="AB3" s="361"/>
+      <c r="AC3" s="361"/>
+      <c r="AD3" s="361"/>
+      <c r="AE3" s="361"/>
+      <c r="AF3" s="361"/>
+      <c r="AG3" s="361"/>
+      <c r="AH3" s="361"/>
+      <c r="AI3" s="361"/>
+      <c r="AJ3" s="361"/>
+      <c r="AK3" s="361"/>
+      <c r="AL3" s="361"/>
+      <c r="AM3" s="361"/>
+      <c r="AN3" s="361"/>
+      <c r="AO3" s="361"/>
+      <c r="AP3" s="361"/>
+      <c r="AQ3" s="361"/>
+      <c r="AR3" s="361"/>
+      <c r="AS3" s="361"/>
+      <c r="AT3" s="361"/>
+      <c r="AU3" s="361"/>
+      <c r="AV3" s="361"/>
+      <c r="AW3" s="361"/>
+      <c r="AX3" s="361"/>
+      <c r="AY3" s="361"/>
+      <c r="AZ3" s="361"/>
+      <c r="BA3" s="361"/>
+      <c r="BB3" s="361"/>
+      <c r="BC3" s="361"/>
+      <c r="BD3" s="361"/>
+      <c r="BE3" s="361"/>
+      <c r="BF3" s="361"/>
+      <c r="BG3" s="361"/>
+      <c r="BH3" s="361"/>
+      <c r="BI3" s="361"/>
+      <c r="BJ3" s="361"/>
+      <c r="BK3" s="361"/>
+      <c r="BL3" s="361"/>
+      <c r="BM3" s="361"/>
+      <c r="BN3" s="361"/>
+      <c r="BO3" s="361"/>
+      <c r="BP3" s="361"/>
+      <c r="BQ3" s="361"/>
+      <c r="BR3" s="361"/>
+      <c r="BS3" s="361"/>
+      <c r="BT3" s="361"/>
+      <c r="BU3" s="361"/>
       <c r="BV3" s="295"/>
-      <c r="BW3" s="388" t="s">
+      <c r="BW3" s="360" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="389"/>
-      <c r="BY3" s="389"/>
-      <c r="BZ3" s="389"/>
-      <c r="CA3" s="389"/>
-      <c r="CB3" s="389"/>
+      <c r="BX3" s="361"/>
+      <c r="BY3" s="361"/>
+      <c r="BZ3" s="361"/>
+      <c r="CA3" s="361"/>
+      <c r="CB3" s="361"/>
       <c r="CC3" s="297"/>
       <c r="CD3" s="297"/>
     </row>
@@ -8352,12 +8355,12 @@
       <c r="BT4" s="298"/>
       <c r="BU4" s="298"/>
       <c r="BV4" s="298"/>
-      <c r="BW4" s="389"/>
-      <c r="BX4" s="389"/>
-      <c r="BY4" s="389"/>
-      <c r="BZ4" s="389"/>
-      <c r="CA4" s="389"/>
-      <c r="CB4" s="389"/>
+      <c r="BW4" s="361"/>
+      <c r="BX4" s="361"/>
+      <c r="BY4" s="361"/>
+      <c r="BZ4" s="361"/>
+      <c r="CA4" s="361"/>
+      <c r="CB4" s="361"/>
       <c r="CC4" s="297"/>
       <c r="CD4" s="297"/>
     </row>
@@ -8435,12 +8438,12 @@
       <c r="BT5" s="298"/>
       <c r="BU5" s="298"/>
       <c r="BV5" s="298"/>
-      <c r="BW5" s="389"/>
-      <c r="BX5" s="389"/>
-      <c r="BY5" s="389"/>
-      <c r="BZ5" s="389"/>
-      <c r="CA5" s="389"/>
-      <c r="CB5" s="389"/>
+      <c r="BW5" s="361"/>
+      <c r="BX5" s="361"/>
+      <c r="BY5" s="361"/>
+      <c r="BZ5" s="361"/>
+      <c r="CA5" s="361"/>
+      <c r="CB5" s="361"/>
       <c r="CC5" s="297"/>
       <c r="CD5" s="297"/>
     </row>
@@ -8516,18 +8519,22 @@
       <c r="BT6" s="300"/>
       <c r="BU6" s="300"/>
       <c r="BV6" s="300"/>
-      <c r="BW6" s="389"/>
-      <c r="BX6" s="389"/>
-      <c r="BY6" s="389"/>
-      <c r="BZ6" s="389"/>
-      <c r="CA6" s="389"/>
-      <c r="CB6" s="389"/>
+      <c r="BW6" s="361"/>
+      <c r="BX6" s="361"/>
+      <c r="BY6" s="361"/>
+      <c r="BZ6" s="361"/>
+      <c r="CA6" s="361"/>
+      <c r="CB6" s="361"/>
       <c r="CC6" s="297"/>
       <c r="CD6" s="297"/>
     </row>
     <row r="7" spans="1:87" s="319" customFormat="1" ht="31" outlineLevel="1">
-      <c r="B7" s="300"/>
-      <c r="C7" s="300"/>
+      <c r="B7" s="300" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="300" t="s">
+        <v>238</v>
+      </c>
       <c r="D7" s="320"/>
       <c r="E7" s="320" t="s">
         <v>155</v>
@@ -8652,359 +8659,361 @@
       <c r="CB7" s="324"/>
       <c r="CC7" s="324"/>
       <c r="CD7" s="324"/>
-      <c r="CE7" s="300"/>
+      <c r="CE7" s="300" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="8" spans="1:87" s="303" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="385" t="s">
+      <c r="A8" s="357" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="394" t="s">
+      <c r="B8" s="371" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="342" t="s">
+      <c r="C8" s="333" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="370" t="s">
+      <c r="D8" s="342" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="370" t="s">
+      <c r="E8" s="342" t="s">
         <v>163</v>
       </c>
-      <c r="F8" s="342" t="s">
+      <c r="F8" s="333" t="s">
         <v>164</v>
       </c>
-      <c r="G8" s="373" t="s">
+      <c r="G8" s="389" t="s">
         <v>165</v>
       </c>
-      <c r="H8" s="373" t="s">
+      <c r="H8" s="389" t="s">
         <v>166</v>
       </c>
-      <c r="I8" s="373" t="s">
+      <c r="I8" s="389" t="s">
         <v>167</v>
       </c>
-      <c r="J8" s="373" t="s">
+      <c r="J8" s="389" t="s">
         <v>168</v>
       </c>
-      <c r="K8" s="383" t="s">
+      <c r="K8" s="387" t="s">
         <v>201</v>
       </c>
-      <c r="L8" s="384"/>
-      <c r="M8" s="384"/>
-      <c r="N8" s="384"/>
-      <c r="O8" s="384"/>
-      <c r="P8" s="384"/>
-      <c r="Q8" s="384"/>
-      <c r="R8" s="384"/>
-      <c r="S8" s="384"/>
-      <c r="T8" s="384"/>
-      <c r="U8" s="384"/>
-      <c r="V8" s="384"/>
-      <c r="W8" s="384"/>
-      <c r="X8" s="384"/>
-      <c r="Y8" s="355" t="s">
+      <c r="L8" s="388"/>
+      <c r="M8" s="388"/>
+      <c r="N8" s="388"/>
+      <c r="O8" s="388"/>
+      <c r="P8" s="388"/>
+      <c r="Q8" s="388"/>
+      <c r="R8" s="388"/>
+      <c r="S8" s="388"/>
+      <c r="T8" s="388"/>
+      <c r="U8" s="388"/>
+      <c r="V8" s="388"/>
+      <c r="W8" s="388"/>
+      <c r="X8" s="388"/>
+      <c r="Y8" s="392" t="s">
         <v>200</v>
       </c>
-      <c r="Z8" s="356"/>
-      <c r="AA8" s="356"/>
-      <c r="AB8" s="356"/>
-      <c r="AC8" s="356"/>
-      <c r="AD8" s="356"/>
-      <c r="AE8" s="356"/>
-      <c r="AF8" s="356"/>
-      <c r="AG8" s="356"/>
-      <c r="AH8" s="356"/>
-      <c r="AI8" s="356"/>
-      <c r="AJ8" s="356"/>
-      <c r="AK8" s="356"/>
-      <c r="AL8" s="356"/>
-      <c r="AM8" s="356"/>
-      <c r="AN8" s="356"/>
-      <c r="AO8" s="357"/>
-      <c r="AP8" s="360" t="s">
+      <c r="Z8" s="393"/>
+      <c r="AA8" s="393"/>
+      <c r="AB8" s="393"/>
+      <c r="AC8" s="393"/>
+      <c r="AD8" s="393"/>
+      <c r="AE8" s="393"/>
+      <c r="AF8" s="393"/>
+      <c r="AG8" s="393"/>
+      <c r="AH8" s="393"/>
+      <c r="AI8" s="393"/>
+      <c r="AJ8" s="393"/>
+      <c r="AK8" s="393"/>
+      <c r="AL8" s="393"/>
+      <c r="AM8" s="393"/>
+      <c r="AN8" s="393"/>
+      <c r="AO8" s="394"/>
+      <c r="AP8" s="354" t="s">
         <v>202</v>
       </c>
-      <c r="AQ8" s="360" t="s">
+      <c r="AQ8" s="354" t="s">
         <v>203</v>
       </c>
-      <c r="AR8" s="360" t="s">
+      <c r="AR8" s="354" t="s">
         <v>204</v>
       </c>
-      <c r="AS8" s="360" t="s">
+      <c r="AS8" s="354" t="s">
         <v>205</v>
       </c>
-      <c r="AT8" s="360" t="s">
+      <c r="AT8" s="354" t="s">
         <v>206</v>
       </c>
-      <c r="AU8" s="360" t="s">
+      <c r="AU8" s="354" t="s">
         <v>207</v>
       </c>
-      <c r="AV8" s="342" t="s">
+      <c r="AV8" s="333" t="s">
         <v>208</v>
       </c>
-      <c r="AW8" s="353" t="s">
+      <c r="AW8" s="365" t="s">
         <v>209</v>
       </c>
-      <c r="AX8" s="342" t="s">
+      <c r="AX8" s="333" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="363" t="s">
+      <c r="AY8" s="395" t="s">
         <v>227</v>
       </c>
-      <c r="AZ8" s="364"/>
-      <c r="BA8" s="364"/>
-      <c r="BB8" s="364"/>
-      <c r="BC8" s="364"/>
-      <c r="BD8" s="364"/>
-      <c r="BE8" s="364"/>
-      <c r="BF8" s="364"/>
-      <c r="BG8" s="364"/>
-      <c r="BH8" s="364"/>
-      <c r="BI8" s="364"/>
-      <c r="BJ8" s="364"/>
-      <c r="BK8" s="364"/>
-      <c r="BL8" s="364"/>
-      <c r="BM8" s="364"/>
-      <c r="BN8" s="364"/>
-      <c r="BO8" s="364"/>
-      <c r="BP8" s="364"/>
-      <c r="BQ8" s="365"/>
-      <c r="BR8" s="345" t="s">
+      <c r="AZ8" s="396"/>
+      <c r="BA8" s="396"/>
+      <c r="BB8" s="396"/>
+      <c r="BC8" s="396"/>
+      <c r="BD8" s="396"/>
+      <c r="BE8" s="396"/>
+      <c r="BF8" s="396"/>
+      <c r="BG8" s="396"/>
+      <c r="BH8" s="396"/>
+      <c r="BI8" s="396"/>
+      <c r="BJ8" s="396"/>
+      <c r="BK8" s="396"/>
+      <c r="BL8" s="396"/>
+      <c r="BM8" s="396"/>
+      <c r="BN8" s="396"/>
+      <c r="BO8" s="396"/>
+      <c r="BP8" s="396"/>
+      <c r="BQ8" s="397"/>
+      <c r="BR8" s="403" t="s">
         <v>224</v>
       </c>
-      <c r="BS8" s="346"/>
-      <c r="BT8" s="342" t="s">
+      <c r="BS8" s="404"/>
+      <c r="BT8" s="333" t="s">
         <v>222</v>
       </c>
-      <c r="BU8" s="339" t="s">
+      <c r="BU8" s="400" t="s">
         <v>223</v>
       </c>
       <c r="BV8" s="328"/>
-      <c r="BW8" s="406" t="s">
+      <c r="BW8" s="336" t="s">
         <v>228</v>
       </c>
-      <c r="BX8" s="397" t="s">
+      <c r="BX8" s="374" t="s">
         <v>237</v>
       </c>
-      <c r="BY8" s="398"/>
-      <c r="BZ8" s="398"/>
-      <c r="CA8" s="399"/>
-      <c r="CB8" s="333" t="s">
+      <c r="BY8" s="375"/>
+      <c r="BZ8" s="375"/>
+      <c r="CA8" s="376"/>
+      <c r="CB8" s="362" t="s">
         <v>233</v>
       </c>
-      <c r="CC8" s="333" t="s">
+      <c r="CC8" s="362" t="s">
         <v>234</v>
       </c>
-      <c r="CD8" s="333" t="s">
+      <c r="CD8" s="362" t="s">
         <v>235</v>
       </c>
       <c r="CH8" s="241"/>
       <c r="CI8" s="241"/>
     </row>
     <row r="9" spans="1:87" s="303" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="386"/>
-      <c r="B9" s="395"/>
-      <c r="C9" s="343"/>
-      <c r="D9" s="371"/>
-      <c r="E9" s="371"/>
-      <c r="F9" s="343"/>
-      <c r="G9" s="374"/>
-      <c r="H9" s="374"/>
-      <c r="I9" s="374"/>
-      <c r="J9" s="374"/>
-      <c r="K9" s="376" t="s">
+      <c r="A9" s="358"/>
+      <c r="B9" s="372"/>
+      <c r="C9" s="334"/>
+      <c r="D9" s="343"/>
+      <c r="E9" s="343"/>
+      <c r="F9" s="334"/>
+      <c r="G9" s="390"/>
+      <c r="H9" s="390"/>
+      <c r="I9" s="390"/>
+      <c r="J9" s="390"/>
+      <c r="K9" s="349" t="s">
         <v>169</v>
       </c>
-      <c r="L9" s="376" t="s">
+      <c r="L9" s="349" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="376" t="s">
+      <c r="M9" s="349" t="s">
         <v>171</v>
       </c>
-      <c r="N9" s="376" t="s">
+      <c r="N9" s="349" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="376" t="s">
+      <c r="O9" s="349" t="s">
         <v>173</v>
       </c>
-      <c r="P9" s="376" t="s">
+      <c r="P9" s="349" t="s">
         <v>174</v>
       </c>
-      <c r="Q9" s="376" t="s">
+      <c r="Q9" s="349" t="s">
         <v>175</v>
       </c>
-      <c r="R9" s="376" t="s">
+      <c r="R9" s="349" t="s">
         <v>176</v>
       </c>
-      <c r="S9" s="376" t="s">
+      <c r="S9" s="349" t="s">
         <v>177</v>
       </c>
-      <c r="T9" s="376" t="s">
+      <c r="T9" s="349" t="s">
         <v>178</v>
       </c>
-      <c r="U9" s="376" t="s">
+      <c r="U9" s="349" t="s">
         <v>179</v>
       </c>
-      <c r="V9" s="379" t="s">
+      <c r="V9" s="383" t="s">
         <v>180</v>
       </c>
-      <c r="W9" s="380"/>
-      <c r="X9" s="376" t="s">
+      <c r="W9" s="384"/>
+      <c r="X9" s="349" t="s">
         <v>183</v>
       </c>
-      <c r="Y9" s="336" t="s">
+      <c r="Y9" s="339" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="336" t="s">
+      <c r="Z9" s="339" t="s">
         <v>184</v>
       </c>
-      <c r="AA9" s="336" t="s">
+      <c r="AA9" s="339" t="s">
         <v>185</v>
       </c>
-      <c r="AB9" s="336" t="s">
+      <c r="AB9" s="339" t="s">
         <v>186</v>
       </c>
-      <c r="AC9" s="336" t="s">
+      <c r="AC9" s="339" t="s">
         <v>187</v>
       </c>
-      <c r="AD9" s="336" t="s">
+      <c r="AD9" s="339" t="s">
         <v>188</v>
       </c>
-      <c r="AE9" s="336" t="s">
+      <c r="AE9" s="339" t="s">
         <v>189</v>
       </c>
-      <c r="AF9" s="336" t="s">
+      <c r="AF9" s="339" t="s">
         <v>190</v>
       </c>
-      <c r="AG9" s="336" t="s">
+      <c r="AG9" s="339" t="s">
         <v>191</v>
       </c>
-      <c r="AH9" s="336" t="s">
+      <c r="AH9" s="339" t="s">
         <v>192</v>
       </c>
-      <c r="AI9" s="336" t="s">
+      <c r="AI9" s="339" t="s">
         <v>193</v>
       </c>
-      <c r="AJ9" s="336" t="s">
+      <c r="AJ9" s="339" t="s">
         <v>194</v>
       </c>
-      <c r="AK9" s="339" t="s">
+      <c r="AK9" s="400" t="s">
         <v>195</v>
       </c>
-      <c r="AL9" s="342" t="s">
+      <c r="AL9" s="333" t="s">
         <v>196</v>
       </c>
-      <c r="AM9" s="336" t="s">
+      <c r="AM9" s="339" t="s">
         <v>197</v>
       </c>
-      <c r="AN9" s="350" t="s">
+      <c r="AN9" s="352" t="s">
         <v>198</v>
       </c>
-      <c r="AO9" s="342" t="s">
+      <c r="AO9" s="333" t="s">
         <v>199</v>
       </c>
-      <c r="AP9" s="361"/>
-      <c r="AQ9" s="361"/>
-      <c r="AR9" s="361"/>
-      <c r="AS9" s="361"/>
-      <c r="AT9" s="361"/>
-      <c r="AU9" s="361"/>
-      <c r="AV9" s="343"/>
-      <c r="AW9" s="390"/>
-      <c r="AX9" s="343"/>
-      <c r="AY9" s="347" t="s">
+      <c r="AP9" s="355"/>
+      <c r="AQ9" s="355"/>
+      <c r="AR9" s="355"/>
+      <c r="AS9" s="355"/>
+      <c r="AT9" s="355"/>
+      <c r="AU9" s="355"/>
+      <c r="AV9" s="334"/>
+      <c r="AW9" s="366"/>
+      <c r="AX9" s="334"/>
+      <c r="AY9" s="405" t="s">
         <v>226</v>
       </c>
-      <c r="AZ9" s="348"/>
-      <c r="BA9" s="348"/>
-      <c r="BB9" s="348"/>
-      <c r="BC9" s="348"/>
-      <c r="BD9" s="348"/>
-      <c r="BE9" s="348"/>
-      <c r="BF9" s="348"/>
-      <c r="BG9" s="348"/>
-      <c r="BH9" s="348"/>
-      <c r="BI9" s="348"/>
-      <c r="BJ9" s="348"/>
-      <c r="BK9" s="348"/>
-      <c r="BL9" s="349"/>
-      <c r="BM9" s="347" t="s">
+      <c r="AZ9" s="406"/>
+      <c r="BA9" s="406"/>
+      <c r="BB9" s="406"/>
+      <c r="BC9" s="406"/>
+      <c r="BD9" s="406"/>
+      <c r="BE9" s="406"/>
+      <c r="BF9" s="406"/>
+      <c r="BG9" s="406"/>
+      <c r="BH9" s="406"/>
+      <c r="BI9" s="406"/>
+      <c r="BJ9" s="406"/>
+      <c r="BK9" s="406"/>
+      <c r="BL9" s="407"/>
+      <c r="BM9" s="405" t="s">
         <v>225</v>
       </c>
-      <c r="BN9" s="348"/>
-      <c r="BO9" s="348"/>
-      <c r="BP9" s="348"/>
-      <c r="BQ9" s="349"/>
-      <c r="BR9" s="343" t="s">
+      <c r="BN9" s="406"/>
+      <c r="BO9" s="406"/>
+      <c r="BP9" s="406"/>
+      <c r="BQ9" s="407"/>
+      <c r="BR9" s="334" t="s">
         <v>65</v>
       </c>
-      <c r="BS9" s="343" t="s">
+      <c r="BS9" s="334" t="s">
         <v>221</v>
       </c>
-      <c r="BT9" s="343"/>
-      <c r="BU9" s="340"/>
+      <c r="BT9" s="334"/>
+      <c r="BU9" s="401"/>
       <c r="BV9" s="328"/>
-      <c r="BW9" s="407"/>
-      <c r="BX9" s="400"/>
-      <c r="BY9" s="401"/>
-      <c r="BZ9" s="401"/>
-      <c r="CA9" s="402"/>
-      <c r="CB9" s="334"/>
-      <c r="CC9" s="334"/>
-      <c r="CD9" s="334"/>
+      <c r="BW9" s="337"/>
+      <c r="BX9" s="377"/>
+      <c r="BY9" s="378"/>
+      <c r="BZ9" s="378"/>
+      <c r="CA9" s="379"/>
+      <c r="CB9" s="363"/>
+      <c r="CC9" s="363"/>
+      <c r="CD9" s="363"/>
       <c r="CH9" s="241"/>
       <c r="CI9" s="241"/>
     </row>
     <row r="10" spans="1:87" s="304" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="386"/>
-      <c r="B10" s="395"/>
-      <c r="C10" s="343"/>
-      <c r="D10" s="371"/>
-      <c r="E10" s="371"/>
-      <c r="F10" s="343"/>
-      <c r="G10" s="374"/>
-      <c r="H10" s="374"/>
-      <c r="I10" s="374"/>
-      <c r="J10" s="374"/>
-      <c r="K10" s="377"/>
-      <c r="L10" s="377"/>
-      <c r="M10" s="377"/>
-      <c r="N10" s="377"/>
-      <c r="O10" s="377"/>
-      <c r="P10" s="377"/>
-      <c r="Q10" s="377"/>
-      <c r="R10" s="377"/>
-      <c r="S10" s="377"/>
-      <c r="T10" s="377"/>
-      <c r="U10" s="377"/>
-      <c r="V10" s="381"/>
-      <c r="W10" s="382"/>
-      <c r="X10" s="377"/>
-      <c r="Y10" s="337"/>
-      <c r="Z10" s="337"/>
-      <c r="AA10" s="337"/>
-      <c r="AB10" s="337"/>
-      <c r="AC10" s="337"/>
-      <c r="AD10" s="337"/>
-      <c r="AE10" s="337"/>
-      <c r="AF10" s="337"/>
-      <c r="AG10" s="337"/>
-      <c r="AH10" s="337"/>
-      <c r="AI10" s="337"/>
-      <c r="AJ10" s="337"/>
-      <c r="AK10" s="340"/>
-      <c r="AL10" s="343"/>
-      <c r="AM10" s="337"/>
-      <c r="AN10" s="351"/>
-      <c r="AO10" s="343"/>
-      <c r="AP10" s="361"/>
-      <c r="AQ10" s="361"/>
-      <c r="AR10" s="361"/>
-      <c r="AS10" s="361"/>
-      <c r="AT10" s="361"/>
-      <c r="AU10" s="361"/>
-      <c r="AV10" s="343"/>
-      <c r="AW10" s="390"/>
-      <c r="AX10" s="343"/>
+      <c r="A10" s="358"/>
+      <c r="B10" s="372"/>
+      <c r="C10" s="334"/>
+      <c r="D10" s="343"/>
+      <c r="E10" s="343"/>
+      <c r="F10" s="334"/>
+      <c r="G10" s="390"/>
+      <c r="H10" s="390"/>
+      <c r="I10" s="390"/>
+      <c r="J10" s="390"/>
+      <c r="K10" s="350"/>
+      <c r="L10" s="350"/>
+      <c r="M10" s="350"/>
+      <c r="N10" s="350"/>
+      <c r="O10" s="350"/>
+      <c r="P10" s="350"/>
+      <c r="Q10" s="350"/>
+      <c r="R10" s="350"/>
+      <c r="S10" s="350"/>
+      <c r="T10" s="350"/>
+      <c r="U10" s="350"/>
+      <c r="V10" s="385"/>
+      <c r="W10" s="386"/>
+      <c r="X10" s="350"/>
+      <c r="Y10" s="340"/>
+      <c r="Z10" s="340"/>
+      <c r="AA10" s="340"/>
+      <c r="AB10" s="340"/>
+      <c r="AC10" s="340"/>
+      <c r="AD10" s="340"/>
+      <c r="AE10" s="340"/>
+      <c r="AF10" s="340"/>
+      <c r="AG10" s="340"/>
+      <c r="AH10" s="340"/>
+      <c r="AI10" s="340"/>
+      <c r="AJ10" s="340"/>
+      <c r="AK10" s="401"/>
+      <c r="AL10" s="334"/>
+      <c r="AM10" s="340"/>
+      <c r="AN10" s="408"/>
+      <c r="AO10" s="334"/>
+      <c r="AP10" s="355"/>
+      <c r="AQ10" s="355"/>
+      <c r="AR10" s="355"/>
+      <c r="AS10" s="355"/>
+      <c r="AT10" s="355"/>
+      <c r="AU10" s="355"/>
+      <c r="AV10" s="334"/>
+      <c r="AW10" s="366"/>
+      <c r="AX10" s="334"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -9014,67 +9023,67 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="392" t="s">
+      <c r="BB10" s="369" t="s">
         <v>210</v>
       </c>
-      <c r="BC10" s="366" t="s">
+      <c r="BC10" s="347" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="366" t="s">
+      <c r="BD10" s="347" t="s">
         <v>211</v>
       </c>
-      <c r="BE10" s="368" t="s">
+      <c r="BE10" s="398" t="s">
         <v>73</v>
       </c>
-      <c r="BF10" s="358" t="s">
+      <c r="BF10" s="345" t="s">
         <v>212</v>
       </c>
-      <c r="BG10" s="358" t="s">
+      <c r="BG10" s="345" t="s">
         <v>213</v>
       </c>
-      <c r="BH10" s="366" t="s">
+      <c r="BH10" s="347" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="366" t="s">
+      <c r="BI10" s="347" t="s">
         <v>214</v>
       </c>
-      <c r="BJ10" s="358" t="s">
+      <c r="BJ10" s="345" t="s">
         <v>215</v>
       </c>
-      <c r="BK10" s="358" t="s">
+      <c r="BK10" s="345" t="s">
         <v>79</v>
       </c>
-      <c r="BL10" s="350" t="s">
+      <c r="BL10" s="352" t="s">
         <v>216</v>
       </c>
-      <c r="BM10" s="366" t="s">
+      <c r="BM10" s="347" t="s">
         <v>217</v>
       </c>
-      <c r="BN10" s="353" t="s">
+      <c r="BN10" s="365" t="s">
         <v>218</v>
       </c>
-      <c r="BO10" s="366" t="s">
+      <c r="BO10" s="347" t="s">
         <v>219</v>
       </c>
-      <c r="BP10" s="353" t="s">
+      <c r="BP10" s="365" t="s">
         <v>220</v>
       </c>
-      <c r="BQ10" s="353" t="s">
+      <c r="BQ10" s="365" t="s">
         <v>85</v>
       </c>
-      <c r="BR10" s="343"/>
-      <c r="BS10" s="343"/>
-      <c r="BT10" s="343"/>
-      <c r="BU10" s="340"/>
+      <c r="BR10" s="334"/>
+      <c r="BS10" s="334"/>
+      <c r="BT10" s="334"/>
+      <c r="BU10" s="401"/>
       <c r="BV10" s="328"/>
-      <c r="BW10" s="408"/>
-      <c r="BX10" s="403"/>
-      <c r="BY10" s="404"/>
-      <c r="BZ10" s="404"/>
-      <c r="CA10" s="405"/>
-      <c r="CB10" s="335"/>
-      <c r="CC10" s="335"/>
-      <c r="CD10" s="335"/>
+      <c r="BW10" s="338"/>
+      <c r="BX10" s="380"/>
+      <c r="BY10" s="381"/>
+      <c r="BZ10" s="381"/>
+      <c r="CA10" s="382"/>
+      <c r="CB10" s="364"/>
+      <c r="CC10" s="364"/>
+      <c r="CD10" s="364"/>
       <c r="CE10" s="318" t="s">
         <v>236</v>
       </c>
@@ -9082,60 +9091,60 @@
       <c r="CI10" s="241"/>
     </row>
     <row r="11" spans="1:87" s="304" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="387"/>
-      <c r="B11" s="396"/>
-      <c r="C11" s="344"/>
-      <c r="D11" s="372"/>
-      <c r="E11" s="372"/>
-      <c r="F11" s="344"/>
-      <c r="G11" s="375"/>
-      <c r="H11" s="375"/>
-      <c r="I11" s="375"/>
-      <c r="J11" s="375"/>
-      <c r="K11" s="378"/>
-      <c r="L11" s="378"/>
-      <c r="M11" s="378"/>
-      <c r="N11" s="378"/>
-      <c r="O11" s="378"/>
-      <c r="P11" s="378"/>
-      <c r="Q11" s="378"/>
-      <c r="R11" s="378"/>
-      <c r="S11" s="378"/>
-      <c r="T11" s="378"/>
-      <c r="U11" s="378"/>
+      <c r="A11" s="359"/>
+      <c r="B11" s="373"/>
+      <c r="C11" s="335"/>
+      <c r="D11" s="344"/>
+      <c r="E11" s="344"/>
+      <c r="F11" s="335"/>
+      <c r="G11" s="391"/>
+      <c r="H11" s="391"/>
+      <c r="I11" s="391"/>
+      <c r="J11" s="391"/>
+      <c r="K11" s="351"/>
+      <c r="L11" s="351"/>
+      <c r="M11" s="351"/>
+      <c r="N11" s="351"/>
+      <c r="O11" s="351"/>
+      <c r="P11" s="351"/>
+      <c r="Q11" s="351"/>
+      <c r="R11" s="351"/>
+      <c r="S11" s="351"/>
+      <c r="T11" s="351"/>
+      <c r="U11" s="351"/>
       <c r="V11" s="330" t="s">
         <v>181</v>
       </c>
       <c r="W11" s="330" t="s">
         <v>182</v>
       </c>
-      <c r="X11" s="378"/>
-      <c r="Y11" s="338"/>
-      <c r="Z11" s="338"/>
-      <c r="AA11" s="338"/>
-      <c r="AB11" s="338"/>
-      <c r="AC11" s="338"/>
-      <c r="AD11" s="338"/>
-      <c r="AE11" s="338"/>
-      <c r="AF11" s="338"/>
-      <c r="AG11" s="338"/>
-      <c r="AH11" s="338"/>
-      <c r="AI11" s="338"/>
-      <c r="AJ11" s="338"/>
-      <c r="AK11" s="341"/>
-      <c r="AL11" s="344"/>
-      <c r="AM11" s="338"/>
-      <c r="AN11" s="352"/>
-      <c r="AO11" s="344"/>
-      <c r="AP11" s="362"/>
-      <c r="AQ11" s="362"/>
-      <c r="AR11" s="362"/>
-      <c r="AS11" s="362"/>
-      <c r="AT11" s="362"/>
-      <c r="AU11" s="362"/>
-      <c r="AV11" s="344"/>
-      <c r="AW11" s="354"/>
-      <c r="AX11" s="344"/>
+      <c r="X11" s="351"/>
+      <c r="Y11" s="341"/>
+      <c r="Z11" s="341"/>
+      <c r="AA11" s="341"/>
+      <c r="AB11" s="341"/>
+      <c r="AC11" s="341"/>
+      <c r="AD11" s="341"/>
+      <c r="AE11" s="341"/>
+      <c r="AF11" s="341"/>
+      <c r="AG11" s="341"/>
+      <c r="AH11" s="341"/>
+      <c r="AI11" s="341"/>
+      <c r="AJ11" s="341"/>
+      <c r="AK11" s="402"/>
+      <c r="AL11" s="335"/>
+      <c r="AM11" s="341"/>
+      <c r="AN11" s="353"/>
+      <c r="AO11" s="335"/>
+      <c r="AP11" s="356"/>
+      <c r="AQ11" s="356"/>
+      <c r="AR11" s="356"/>
+      <c r="AS11" s="356"/>
+      <c r="AT11" s="356"/>
+      <c r="AU11" s="356"/>
+      <c r="AV11" s="335"/>
+      <c r="AW11" s="367"/>
+      <c r="AX11" s="335"/>
       <c r="AY11" s="329" t="s">
         <v>88</v>
       </c>
@@ -9145,28 +9154,28 @@
       <c r="BA11" s="329" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="393"/>
-      <c r="BC11" s="367"/>
-      <c r="BD11" s="367"/>
-      <c r="BE11" s="369"/>
-      <c r="BF11" s="359"/>
-      <c r="BG11" s="359"/>
-      <c r="BH11" s="367"/>
-      <c r="BI11" s="367"/>
-      <c r="BJ11" s="359"/>
-      <c r="BK11" s="359"/>
-      <c r="BL11" s="352"/>
-      <c r="BM11" s="367"/>
-      <c r="BN11" s="354"/>
-      <c r="BO11" s="367"/>
-      <c r="BP11" s="354"/>
-      <c r="BQ11" s="354"/>
-      <c r="BR11" s="344"/>
-      <c r="BS11" s="344"/>
-      <c r="BT11" s="344"/>
-      <c r="BU11" s="341"/>
+      <c r="BB11" s="370"/>
+      <c r="BC11" s="348"/>
+      <c r="BD11" s="348"/>
+      <c r="BE11" s="399"/>
+      <c r="BF11" s="346"/>
+      <c r="BG11" s="346"/>
+      <c r="BH11" s="348"/>
+      <c r="BI11" s="348"/>
+      <c r="BJ11" s="346"/>
+      <c r="BK11" s="346"/>
+      <c r="BL11" s="353"/>
+      <c r="BM11" s="348"/>
+      <c r="BN11" s="367"/>
+      <c r="BO11" s="348"/>
+      <c r="BP11" s="367"/>
+      <c r="BQ11" s="367"/>
+      <c r="BR11" s="335"/>
+      <c r="BS11" s="335"/>
+      <c r="BT11" s="335"/>
+      <c r="BU11" s="402"/>
       <c r="BV11" s="328"/>
-      <c r="BW11" s="408"/>
+      <c r="BW11" s="338"/>
       <c r="BX11" s="326" t="s">
         <v>229</v>
       </c>
@@ -9179,9 +9188,9 @@
       <c r="CA11" s="331" t="s">
         <v>232</v>
       </c>
-      <c r="CB11" s="335"/>
-      <c r="CC11" s="335"/>
-      <c r="CD11" s="335"/>
+      <c r="CB11" s="364"/>
+      <c r="CC11" s="364"/>
+      <c r="CD11" s="364"/>
       <c r="CE11" s="317">
         <v>26</v>
       </c>
@@ -11641,6 +11650,72 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="BR8:BS8"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BX8:CA10"/>
     <mergeCell ref="C8:C11"/>
     <mergeCell ref="BW8:BW11"/>
     <mergeCell ref="AI9:AI11"/>
@@ -11657,72 +11732,6 @@
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="AF9:AF11"/>
     <mergeCell ref="R9:R11"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="AB9:AB11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B5 B7 B15:B25 B37:B1048576 B27:B35 B12:BU12">
     <cfRule type="duplicateValues" dxfId="26" priority="84"/>
@@ -11936,87 +11945,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="438"/>
-      <c r="B3" s="429"/>
-      <c r="C3" s="429"/>
-      <c r="D3" s="429"/>
-      <c r="E3" s="429"/>
-      <c r="F3" s="429"/>
-      <c r="G3" s="429"/>
-      <c r="H3" s="429"/>
-      <c r="I3" s="429"/>
-      <c r="J3" s="429"/>
-      <c r="K3" s="429"/>
-      <c r="L3" s="429"/>
-      <c r="M3" s="429"/>
-      <c r="N3" s="429"/>
-      <c r="O3" s="429"/>
-      <c r="P3" s="429"/>
-      <c r="Q3" s="429"/>
-      <c r="R3" s="429"/>
-      <c r="S3" s="429"/>
-      <c r="T3" s="429"/>
-      <c r="U3" s="429"/>
-      <c r="V3" s="429"/>
-      <c r="W3" s="429"/>
-      <c r="X3" s="429"/>
-      <c r="Y3" s="429"/>
-      <c r="Z3" s="429"/>
-      <c r="AA3" s="429"/>
-      <c r="AB3" s="429"/>
-      <c r="AC3" s="429"/>
-      <c r="AD3" s="429"/>
-      <c r="AE3" s="429"/>
-      <c r="AF3" s="429"/>
-      <c r="AG3" s="429"/>
-      <c r="AH3" s="429"/>
-      <c r="AI3" s="429"/>
-      <c r="AJ3" s="429"/>
-      <c r="AK3" s="429"/>
-      <c r="AL3" s="429"/>
-      <c r="AM3" s="429"/>
-      <c r="AN3" s="429"/>
-      <c r="AO3" s="429"/>
-      <c r="AP3" s="429"/>
-      <c r="AQ3" s="429"/>
-      <c r="AR3" s="429"/>
-      <c r="AS3" s="429"/>
-      <c r="AT3" s="429"/>
-      <c r="AU3" s="429"/>
-      <c r="AV3" s="429"/>
-      <c r="AW3" s="429"/>
-      <c r="AX3" s="429"/>
-      <c r="AY3" s="429"/>
-      <c r="AZ3" s="429"/>
-      <c r="BA3" s="429"/>
-      <c r="BB3" s="429"/>
-      <c r="BC3" s="429"/>
-      <c r="BD3" s="429"/>
-      <c r="BE3" s="429"/>
-      <c r="BF3" s="429"/>
-      <c r="BG3" s="429"/>
-      <c r="BH3" s="429"/>
-      <c r="BI3" s="429"/>
-      <c r="BJ3" s="429"/>
-      <c r="BK3" s="429"/>
-      <c r="BL3" s="429"/>
-      <c r="BM3" s="429"/>
-      <c r="BN3" s="429"/>
-      <c r="BO3" s="429"/>
-      <c r="BP3" s="429"/>
-      <c r="BQ3" s="429"/>
-      <c r="BR3" s="429"/>
-      <c r="BS3" s="429"/>
-      <c r="BT3" s="429"/>
-      <c r="BU3" s="429"/>
-      <c r="BW3" s="428" t="s">
+      <c r="A3" s="442"/>
+      <c r="B3" s="431"/>
+      <c r="C3" s="431"/>
+      <c r="D3" s="431"/>
+      <c r="E3" s="431"/>
+      <c r="F3" s="431"/>
+      <c r="G3" s="431"/>
+      <c r="H3" s="431"/>
+      <c r="I3" s="431"/>
+      <c r="J3" s="431"/>
+      <c r="K3" s="431"/>
+      <c r="L3" s="431"/>
+      <c r="M3" s="431"/>
+      <c r="N3" s="431"/>
+      <c r="O3" s="431"/>
+      <c r="P3" s="431"/>
+      <c r="Q3" s="431"/>
+      <c r="R3" s="431"/>
+      <c r="S3" s="431"/>
+      <c r="T3" s="431"/>
+      <c r="U3" s="431"/>
+      <c r="V3" s="431"/>
+      <c r="W3" s="431"/>
+      <c r="X3" s="431"/>
+      <c r="Y3" s="431"/>
+      <c r="Z3" s="431"/>
+      <c r="AA3" s="431"/>
+      <c r="AB3" s="431"/>
+      <c r="AC3" s="431"/>
+      <c r="AD3" s="431"/>
+      <c r="AE3" s="431"/>
+      <c r="AF3" s="431"/>
+      <c r="AG3" s="431"/>
+      <c r="AH3" s="431"/>
+      <c r="AI3" s="431"/>
+      <c r="AJ3" s="431"/>
+      <c r="AK3" s="431"/>
+      <c r="AL3" s="431"/>
+      <c r="AM3" s="431"/>
+      <c r="AN3" s="431"/>
+      <c r="AO3" s="431"/>
+      <c r="AP3" s="431"/>
+      <c r="AQ3" s="431"/>
+      <c r="AR3" s="431"/>
+      <c r="AS3" s="431"/>
+      <c r="AT3" s="431"/>
+      <c r="AU3" s="431"/>
+      <c r="AV3" s="431"/>
+      <c r="AW3" s="431"/>
+      <c r="AX3" s="431"/>
+      <c r="AY3" s="431"/>
+      <c r="AZ3" s="431"/>
+      <c r="BA3" s="431"/>
+      <c r="BB3" s="431"/>
+      <c r="BC3" s="431"/>
+      <c r="BD3" s="431"/>
+      <c r="BE3" s="431"/>
+      <c r="BF3" s="431"/>
+      <c r="BG3" s="431"/>
+      <c r="BH3" s="431"/>
+      <c r="BI3" s="431"/>
+      <c r="BJ3" s="431"/>
+      <c r="BK3" s="431"/>
+      <c r="BL3" s="431"/>
+      <c r="BM3" s="431"/>
+      <c r="BN3" s="431"/>
+      <c r="BO3" s="431"/>
+      <c r="BP3" s="431"/>
+      <c r="BQ3" s="431"/>
+      <c r="BR3" s="431"/>
+      <c r="BS3" s="431"/>
+      <c r="BT3" s="431"/>
+      <c r="BU3" s="431"/>
+      <c r="BW3" s="430" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="429"/>
-      <c r="BY3" s="429"/>
-      <c r="BZ3" s="429"/>
-      <c r="CA3" s="429"/>
-      <c r="CB3" s="429"/>
+      <c r="BX3" s="431"/>
+      <c r="BY3" s="431"/>
+      <c r="BZ3" s="431"/>
+      <c r="CA3" s="431"/>
+      <c r="CB3" s="431"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -12099,364 +12108,364 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="429"/>
-      <c r="BX4" s="429"/>
-      <c r="BY4" s="429"/>
-      <c r="BZ4" s="429"/>
-      <c r="CA4" s="429"/>
-      <c r="CB4" s="429"/>
+      <c r="BW4" s="431"/>
+      <c r="BX4" s="431"/>
+      <c r="BY4" s="431"/>
+      <c r="BZ4" s="431"/>
+      <c r="CA4" s="431"/>
+      <c r="CB4" s="431"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="441" t="s">
+      <c r="A5" s="418" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="440" t="s">
+      <c r="B5" s="429" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="413" t="s">
+      <c r="C5" s="417" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="439" t="s">
+      <c r="D5" s="424" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="439" t="s">
+      <c r="E5" s="424" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="413" t="s">
+      <c r="F5" s="417" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="413" t="s">
+      <c r="G5" s="417" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="417" t="s">
+      <c r="H5" s="415" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="417" t="s">
+      <c r="I5" s="415" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="413" t="s">
+      <c r="J5" s="417" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="443" t="s">
+      <c r="K5" s="422" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="425"/>
-      <c r="M5" s="425"/>
-      <c r="N5" s="425"/>
-      <c r="O5" s="425"/>
-      <c r="P5" s="425"/>
-      <c r="Q5" s="425"/>
-      <c r="R5" s="425"/>
-      <c r="S5" s="425"/>
-      <c r="T5" s="425"/>
-      <c r="U5" s="425"/>
-      <c r="V5" s="425"/>
-      <c r="W5" s="425"/>
-      <c r="X5" s="425"/>
-      <c r="Y5" s="413" t="s">
+      <c r="L5" s="413"/>
+      <c r="M5" s="413"/>
+      <c r="N5" s="413"/>
+      <c r="O5" s="413"/>
+      <c r="P5" s="413"/>
+      <c r="Q5" s="413"/>
+      <c r="R5" s="413"/>
+      <c r="S5" s="413"/>
+      <c r="T5" s="413"/>
+      <c r="U5" s="413"/>
+      <c r="V5" s="413"/>
+      <c r="W5" s="413"/>
+      <c r="X5" s="413"/>
+      <c r="Y5" s="417" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="425"/>
-      <c r="AA5" s="425"/>
-      <c r="AB5" s="425"/>
-      <c r="AC5" s="425"/>
-      <c r="AD5" s="425"/>
-      <c r="AE5" s="425"/>
-      <c r="AF5" s="425"/>
-      <c r="AG5" s="425"/>
-      <c r="AH5" s="425"/>
-      <c r="AI5" s="425"/>
-      <c r="AJ5" s="425"/>
-      <c r="AK5" s="425"/>
-      <c r="AL5" s="425"/>
-      <c r="AM5" s="425"/>
-      <c r="AN5" s="425"/>
-      <c r="AO5" s="426"/>
-      <c r="AP5" s="413" t="s">
+      <c r="Z5" s="413"/>
+      <c r="AA5" s="413"/>
+      <c r="AB5" s="413"/>
+      <c r="AC5" s="413"/>
+      <c r="AD5" s="413"/>
+      <c r="AE5" s="413"/>
+      <c r="AF5" s="413"/>
+      <c r="AG5" s="413"/>
+      <c r="AH5" s="413"/>
+      <c r="AI5" s="413"/>
+      <c r="AJ5" s="413"/>
+      <c r="AK5" s="413"/>
+      <c r="AL5" s="413"/>
+      <c r="AM5" s="413"/>
+      <c r="AN5" s="413"/>
+      <c r="AO5" s="414"/>
+      <c r="AP5" s="417" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="413" t="s">
+      <c r="AQ5" s="417" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="413" t="s">
+      <c r="AR5" s="417" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="413" t="s">
+      <c r="AS5" s="417" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="413" t="s">
+      <c r="AT5" s="417" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="413" t="s">
+      <c r="AU5" s="417" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="413" t="s">
+      <c r="AV5" s="417" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="413" t="s">
+      <c r="AW5" s="417" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="413" t="s">
+      <c r="AX5" s="417" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="424" t="s">
+      <c r="AY5" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="425"/>
-      <c r="BA5" s="425"/>
-      <c r="BB5" s="425"/>
-      <c r="BC5" s="425"/>
-      <c r="BD5" s="425"/>
-      <c r="BE5" s="425"/>
-      <c r="BF5" s="425"/>
-      <c r="BG5" s="425"/>
-      <c r="BH5" s="425"/>
-      <c r="BI5" s="425"/>
-      <c r="BJ5" s="425"/>
-      <c r="BK5" s="425"/>
-      <c r="BL5" s="425"/>
-      <c r="BM5" s="425"/>
-      <c r="BN5" s="425"/>
-      <c r="BO5" s="425"/>
-      <c r="BP5" s="425"/>
-      <c r="BQ5" s="426"/>
-      <c r="BR5" s="430" t="s">
+      <c r="AZ5" s="413"/>
+      <c r="BA5" s="413"/>
+      <c r="BB5" s="413"/>
+      <c r="BC5" s="413"/>
+      <c r="BD5" s="413"/>
+      <c r="BE5" s="413"/>
+      <c r="BF5" s="413"/>
+      <c r="BG5" s="413"/>
+      <c r="BH5" s="413"/>
+      <c r="BI5" s="413"/>
+      <c r="BJ5" s="413"/>
+      <c r="BK5" s="413"/>
+      <c r="BL5" s="413"/>
+      <c r="BM5" s="413"/>
+      <c r="BN5" s="413"/>
+      <c r="BO5" s="413"/>
+      <c r="BP5" s="413"/>
+      <c r="BQ5" s="414"/>
+      <c r="BR5" s="433" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="431"/>
-      <c r="BT5" s="424" t="s">
+      <c r="BS5" s="427"/>
+      <c r="BT5" s="412" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="418" t="s">
+      <c r="BU5" s="444" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="421" t="s">
+      <c r="BW5" s="445" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="432" t="s">
+      <c r="BX5" s="434" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="433"/>
-      <c r="BZ5" s="433"/>
-      <c r="CA5" s="431"/>
-      <c r="CB5" s="427" t="s">
+      <c r="BY5" s="435"/>
+      <c r="BZ5" s="435"/>
+      <c r="CA5" s="427"/>
+      <c r="CB5" s="446" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="333" t="s">
+      <c r="CC5" s="362" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="333" t="s">
+      <c r="CD5" s="362" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="409"/>
-      <c r="B6" s="409"/>
-      <c r="C6" s="409"/>
-      <c r="D6" s="409"/>
-      <c r="E6" s="409"/>
-      <c r="F6" s="409"/>
-      <c r="G6" s="409"/>
-      <c r="H6" s="409"/>
-      <c r="I6" s="409"/>
-      <c r="J6" s="409"/>
-      <c r="K6" s="414" t="s">
+      <c r="A6" s="410"/>
+      <c r="B6" s="410"/>
+      <c r="C6" s="410"/>
+      <c r="D6" s="410"/>
+      <c r="E6" s="410"/>
+      <c r="F6" s="410"/>
+      <c r="G6" s="410"/>
+      <c r="H6" s="410"/>
+      <c r="I6" s="410"/>
+      <c r="J6" s="410"/>
+      <c r="K6" s="425" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="414" t="s">
+      <c r="L6" s="425" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="414" t="s">
+      <c r="M6" s="425" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="414" t="s">
+      <c r="N6" s="425" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="414" t="s">
+      <c r="O6" s="425" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="414" t="s">
+      <c r="P6" s="425" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="414" t="s">
+      <c r="Q6" s="425" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="414" t="s">
+      <c r="R6" s="425" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="414" t="s">
+      <c r="S6" s="425" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="414" t="s">
+      <c r="T6" s="425" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="414" t="s">
+      <c r="U6" s="425" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="445" t="s">
+      <c r="V6" s="426" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="431"/>
-      <c r="X6" s="414" t="s">
+      <c r="W6" s="427"/>
+      <c r="X6" s="425" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="413" t="s">
+      <c r="Y6" s="417" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="413" t="s">
+      <c r="Z6" s="417" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="413" t="s">
+      <c r="AA6" s="417" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="413" t="s">
+      <c r="AB6" s="417" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="417" t="s">
+      <c r="AC6" s="415" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="417" t="s">
+      <c r="AD6" s="415" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="417" t="s">
+      <c r="AE6" s="415" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="417" t="s">
+      <c r="AF6" s="415" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="413" t="s">
+      <c r="AG6" s="417" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="417" t="s">
+      <c r="AH6" s="415" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="417" t="s">
+      <c r="AI6" s="415" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="413" t="s">
+      <c r="AJ6" s="417" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="442" t="s">
+      <c r="AK6" s="419" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="413" t="s">
+      <c r="AL6" s="417" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="413" t="s">
+      <c r="AM6" s="417" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="444" t="s">
+      <c r="AN6" s="423" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="413" t="s">
+      <c r="AO6" s="417" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="409"/>
-      <c r="AQ6" s="409"/>
-      <c r="AR6" s="409"/>
-      <c r="AS6" s="409"/>
-      <c r="AT6" s="409"/>
-      <c r="AU6" s="409"/>
-      <c r="AV6" s="409"/>
-      <c r="AW6" s="409"/>
-      <c r="AX6" s="409"/>
-      <c r="AY6" s="424" t="s">
+      <c r="AP6" s="410"/>
+      <c r="AQ6" s="410"/>
+      <c r="AR6" s="410"/>
+      <c r="AS6" s="410"/>
+      <c r="AT6" s="410"/>
+      <c r="AU6" s="410"/>
+      <c r="AV6" s="410"/>
+      <c r="AW6" s="410"/>
+      <c r="AX6" s="410"/>
+      <c r="AY6" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="425"/>
-      <c r="BA6" s="425"/>
-      <c r="BB6" s="425"/>
-      <c r="BC6" s="425"/>
-      <c r="BD6" s="425"/>
-      <c r="BE6" s="425"/>
-      <c r="BF6" s="425"/>
-      <c r="BG6" s="425"/>
-      <c r="BH6" s="425"/>
-      <c r="BI6" s="425"/>
-      <c r="BJ6" s="425"/>
-      <c r="BK6" s="425"/>
-      <c r="BL6" s="426"/>
-      <c r="BM6" s="424" t="s">
+      <c r="AZ6" s="413"/>
+      <c r="BA6" s="413"/>
+      <c r="BB6" s="413"/>
+      <c r="BC6" s="413"/>
+      <c r="BD6" s="413"/>
+      <c r="BE6" s="413"/>
+      <c r="BF6" s="413"/>
+      <c r="BG6" s="413"/>
+      <c r="BH6" s="413"/>
+      <c r="BI6" s="413"/>
+      <c r="BJ6" s="413"/>
+      <c r="BK6" s="413"/>
+      <c r="BL6" s="414"/>
+      <c r="BM6" s="412" t="s">
         <v>64</v>
       </c>
-      <c r="BN6" s="425"/>
-      <c r="BO6" s="425"/>
-      <c r="BP6" s="425"/>
-      <c r="BQ6" s="426"/>
-      <c r="BR6" s="411" t="s">
+      <c r="BN6" s="413"/>
+      <c r="BO6" s="413"/>
+      <c r="BP6" s="413"/>
+      <c r="BQ6" s="414"/>
+      <c r="BR6" s="409" t="s">
         <v>65</v>
       </c>
-      <c r="BS6" s="411" t="s">
+      <c r="BS6" s="409" t="s">
         <v>66</v>
       </c>
-      <c r="BT6" s="409"/>
-      <c r="BU6" s="419"/>
-      <c r="BW6" s="422"/>
-      <c r="BX6" s="419"/>
-      <c r="BY6" s="434"/>
-      <c r="BZ6" s="434"/>
-      <c r="CA6" s="422"/>
-      <c r="CB6" s="409"/>
-      <c r="CC6" s="409"/>
-      <c r="CD6" s="409"/>
+      <c r="BT6" s="410"/>
+      <c r="BU6" s="420"/>
+      <c r="BW6" s="437"/>
+      <c r="BX6" s="420"/>
+      <c r="BY6" s="436"/>
+      <c r="BZ6" s="436"/>
+      <c r="CA6" s="437"/>
+      <c r="CB6" s="410"/>
+      <c r="CC6" s="410"/>
+      <c r="CD6" s="410"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A7" s="409"/>
-      <c r="B7" s="409"/>
-      <c r="C7" s="409"/>
-      <c r="D7" s="409"/>
-      <c r="E7" s="409"/>
-      <c r="F7" s="409"/>
-      <c r="G7" s="409"/>
-      <c r="H7" s="409"/>
-      <c r="I7" s="409"/>
-      <c r="J7" s="409"/>
-      <c r="K7" s="409"/>
-      <c r="L7" s="409"/>
-      <c r="M7" s="409"/>
-      <c r="N7" s="409"/>
-      <c r="O7" s="409"/>
-      <c r="P7" s="409"/>
-      <c r="Q7" s="409"/>
-      <c r="R7" s="409"/>
-      <c r="S7" s="409"/>
-      <c r="T7" s="409"/>
-      <c r="U7" s="409"/>
-      <c r="V7" s="420"/>
-      <c r="W7" s="446"/>
-      <c r="X7" s="409"/>
-      <c r="Y7" s="409"/>
-      <c r="Z7" s="409"/>
-      <c r="AA7" s="409"/>
-      <c r="AB7" s="409"/>
-      <c r="AC7" s="409"/>
-      <c r="AD7" s="409"/>
-      <c r="AE7" s="409"/>
-      <c r="AF7" s="409"/>
-      <c r="AG7" s="409"/>
-      <c r="AH7" s="409"/>
-      <c r="AI7" s="409"/>
-      <c r="AJ7" s="409"/>
-      <c r="AK7" s="419"/>
-      <c r="AL7" s="409"/>
-      <c r="AM7" s="409"/>
-      <c r="AN7" s="409"/>
-      <c r="AO7" s="409"/>
-      <c r="AP7" s="409"/>
-      <c r="AQ7" s="409"/>
-      <c r="AR7" s="409"/>
-      <c r="AS7" s="409"/>
-      <c r="AT7" s="409"/>
-      <c r="AU7" s="409"/>
-      <c r="AV7" s="409"/>
-      <c r="AW7" s="409"/>
-      <c r="AX7" s="409"/>
+      <c r="A7" s="410"/>
+      <c r="B7" s="410"/>
+      <c r="C7" s="410"/>
+      <c r="D7" s="410"/>
+      <c r="E7" s="410"/>
+      <c r="F7" s="410"/>
+      <c r="G7" s="410"/>
+      <c r="H7" s="410"/>
+      <c r="I7" s="410"/>
+      <c r="J7" s="410"/>
+      <c r="K7" s="410"/>
+      <c r="L7" s="410"/>
+      <c r="M7" s="410"/>
+      <c r="N7" s="410"/>
+      <c r="O7" s="410"/>
+      <c r="P7" s="410"/>
+      <c r="Q7" s="410"/>
+      <c r="R7" s="410"/>
+      <c r="S7" s="410"/>
+      <c r="T7" s="410"/>
+      <c r="U7" s="410"/>
+      <c r="V7" s="421"/>
+      <c r="W7" s="428"/>
+      <c r="X7" s="410"/>
+      <c r="Y7" s="410"/>
+      <c r="Z7" s="410"/>
+      <c r="AA7" s="410"/>
+      <c r="AB7" s="410"/>
+      <c r="AC7" s="410"/>
+      <c r="AD7" s="410"/>
+      <c r="AE7" s="410"/>
+      <c r="AF7" s="410"/>
+      <c r="AG7" s="410"/>
+      <c r="AH7" s="410"/>
+      <c r="AI7" s="410"/>
+      <c r="AJ7" s="410"/>
+      <c r="AK7" s="420"/>
+      <c r="AL7" s="410"/>
+      <c r="AM7" s="410"/>
+      <c r="AN7" s="410"/>
+      <c r="AO7" s="410"/>
+      <c r="AP7" s="410"/>
+      <c r="AQ7" s="410"/>
+      <c r="AR7" s="410"/>
+      <c r="AS7" s="410"/>
+      <c r="AT7" s="410"/>
+      <c r="AU7" s="410"/>
+      <c r="AV7" s="410"/>
+      <c r="AW7" s="410"/>
+      <c r="AX7" s="410"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -12466,124 +12475,124 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="424" t="s">
+      <c r="BB7" s="412" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="415" t="s">
+      <c r="BC7" s="416" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="415" t="s">
+      <c r="BD7" s="416" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="437" t="s">
+      <c r="BE7" s="441" t="s">
         <v>73</v>
       </c>
-      <c r="BF7" s="415" t="s">
+      <c r="BF7" s="416" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="415" t="s">
+      <c r="BG7" s="416" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="415" t="s">
+      <c r="BH7" s="416" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="415" t="s">
+      <c r="BI7" s="416" t="s">
         <v>77</v>
       </c>
-      <c r="BJ7" s="415" t="s">
+      <c r="BJ7" s="416" t="s">
         <v>78</v>
       </c>
-      <c r="BK7" s="415" t="s">
+      <c r="BK7" s="416" t="s">
         <v>79</v>
       </c>
-      <c r="BL7" s="416" t="s">
+      <c r="BL7" s="443" t="s">
         <v>80</v>
       </c>
-      <c r="BM7" s="415" t="s">
+      <c r="BM7" s="416" t="s">
         <v>81</v>
       </c>
-      <c r="BN7" s="424" t="s">
+      <c r="BN7" s="412" t="s">
         <v>82</v>
       </c>
-      <c r="BO7" s="415" t="s">
+      <c r="BO7" s="416" t="s">
         <v>83</v>
       </c>
-      <c r="BP7" s="424" t="s">
+      <c r="BP7" s="412" t="s">
         <v>84</v>
       </c>
-      <c r="BQ7" s="424" t="s">
+      <c r="BQ7" s="412" t="s">
         <v>85</v>
       </c>
-      <c r="BR7" s="409"/>
-      <c r="BS7" s="409"/>
-      <c r="BT7" s="409"/>
-      <c r="BU7" s="419"/>
-      <c r="BW7" s="422"/>
-      <c r="BX7" s="435"/>
-      <c r="BY7" s="436"/>
-      <c r="BZ7" s="436"/>
-      <c r="CA7" s="423"/>
-      <c r="CB7" s="409"/>
-      <c r="CC7" s="409"/>
-      <c r="CD7" s="409"/>
+      <c r="BR7" s="410"/>
+      <c r="BS7" s="410"/>
+      <c r="BT7" s="410"/>
+      <c r="BU7" s="420"/>
+      <c r="BW7" s="437"/>
+      <c r="BX7" s="438"/>
+      <c r="BY7" s="439"/>
+      <c r="BZ7" s="439"/>
+      <c r="CA7" s="440"/>
+      <c r="CB7" s="410"/>
+      <c r="CC7" s="410"/>
+      <c r="CD7" s="410"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="139" customFormat="1" ht="12">
-      <c r="A8" s="412"/>
-      <c r="B8" s="412"/>
-      <c r="C8" s="412"/>
-      <c r="D8" s="412"/>
-      <c r="E8" s="412"/>
-      <c r="F8" s="412"/>
-      <c r="G8" s="412"/>
-      <c r="H8" s="412"/>
-      <c r="I8" s="412"/>
-      <c r="J8" s="412"/>
-      <c r="K8" s="412"/>
-      <c r="L8" s="412"/>
-      <c r="M8" s="412"/>
-      <c r="N8" s="412"/>
-      <c r="O8" s="412"/>
-      <c r="P8" s="412"/>
-      <c r="Q8" s="412"/>
-      <c r="R8" s="412"/>
-      <c r="S8" s="412"/>
-      <c r="T8" s="412"/>
-      <c r="U8" s="412"/>
+      <c r="A8" s="411"/>
+      <c r="B8" s="411"/>
+      <c r="C8" s="411"/>
+      <c r="D8" s="411"/>
+      <c r="E8" s="411"/>
+      <c r="F8" s="411"/>
+      <c r="G8" s="411"/>
+      <c r="H8" s="411"/>
+      <c r="I8" s="411"/>
+      <c r="J8" s="411"/>
+      <c r="K8" s="411"/>
+      <c r="L8" s="411"/>
+      <c r="M8" s="411"/>
+      <c r="N8" s="411"/>
+      <c r="O8" s="411"/>
+      <c r="P8" s="411"/>
+      <c r="Q8" s="411"/>
+      <c r="R8" s="411"/>
+      <c r="S8" s="411"/>
+      <c r="T8" s="411"/>
+      <c r="U8" s="411"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="412"/>
-      <c r="Y8" s="412"/>
-      <c r="Z8" s="412"/>
-      <c r="AA8" s="412"/>
-      <c r="AB8" s="412"/>
-      <c r="AC8" s="412"/>
-      <c r="AD8" s="412"/>
-      <c r="AE8" s="412"/>
-      <c r="AF8" s="412"/>
-      <c r="AG8" s="412"/>
-      <c r="AH8" s="412"/>
-      <c r="AI8" s="412"/>
-      <c r="AJ8" s="412"/>
-      <c r="AK8" s="420"/>
-      <c r="AL8" s="412"/>
-      <c r="AM8" s="412"/>
-      <c r="AN8" s="412"/>
-      <c r="AO8" s="412"/>
-      <c r="AP8" s="412"/>
-      <c r="AQ8" s="412"/>
-      <c r="AR8" s="412"/>
-      <c r="AS8" s="412"/>
-      <c r="AT8" s="412"/>
-      <c r="AU8" s="412"/>
-      <c r="AV8" s="412"/>
-      <c r="AW8" s="412"/>
-      <c r="AX8" s="412"/>
+      <c r="X8" s="411"/>
+      <c r="Y8" s="411"/>
+      <c r="Z8" s="411"/>
+      <c r="AA8" s="411"/>
+      <c r="AB8" s="411"/>
+      <c r="AC8" s="411"/>
+      <c r="AD8" s="411"/>
+      <c r="AE8" s="411"/>
+      <c r="AF8" s="411"/>
+      <c r="AG8" s="411"/>
+      <c r="AH8" s="411"/>
+      <c r="AI8" s="411"/>
+      <c r="AJ8" s="411"/>
+      <c r="AK8" s="421"/>
+      <c r="AL8" s="411"/>
+      <c r="AM8" s="411"/>
+      <c r="AN8" s="411"/>
+      <c r="AO8" s="411"/>
+      <c r="AP8" s="411"/>
+      <c r="AQ8" s="411"/>
+      <c r="AR8" s="411"/>
+      <c r="AS8" s="411"/>
+      <c r="AT8" s="411"/>
+      <c r="AU8" s="411"/>
+      <c r="AV8" s="411"/>
+      <c r="AW8" s="411"/>
+      <c r="AX8" s="411"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -12593,27 +12602,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="412"/>
-      <c r="BC8" s="412"/>
-      <c r="BD8" s="412"/>
-      <c r="BE8" s="412"/>
-      <c r="BF8" s="412"/>
-      <c r="BG8" s="412"/>
-      <c r="BH8" s="412"/>
-      <c r="BI8" s="412"/>
-      <c r="BJ8" s="412"/>
-      <c r="BK8" s="412"/>
-      <c r="BL8" s="412"/>
-      <c r="BM8" s="412"/>
-      <c r="BN8" s="412"/>
-      <c r="BO8" s="412"/>
-      <c r="BP8" s="412"/>
-      <c r="BQ8" s="412"/>
-      <c r="BR8" s="412"/>
-      <c r="BS8" s="412"/>
-      <c r="BT8" s="412"/>
-      <c r="BU8" s="420"/>
-      <c r="BW8" s="423"/>
+      <c r="BB8" s="411"/>
+      <c r="BC8" s="411"/>
+      <c r="BD8" s="411"/>
+      <c r="BE8" s="411"/>
+      <c r="BF8" s="411"/>
+      <c r="BG8" s="411"/>
+      <c r="BH8" s="411"/>
+      <c r="BI8" s="411"/>
+      <c r="BJ8" s="411"/>
+      <c r="BK8" s="411"/>
+      <c r="BL8" s="411"/>
+      <c r="BM8" s="411"/>
+      <c r="BN8" s="411"/>
+      <c r="BO8" s="411"/>
+      <c r="BP8" s="411"/>
+      <c r="BQ8" s="411"/>
+      <c r="BR8" s="411"/>
+      <c r="BS8" s="411"/>
+      <c r="BT8" s="411"/>
+      <c r="BU8" s="421"/>
+      <c r="BW8" s="440"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -12626,9 +12635,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="410"/>
-      <c r="CC8" s="410"/>
-      <c r="CD8" s="410"/>
+      <c r="CB8" s="432"/>
+      <c r="CC8" s="432"/>
+      <c r="CD8" s="432"/>
       <c r="CE8" s="136"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
@@ -15086,6 +15095,72 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="82">
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="BS6:BS8"/>
     <mergeCell ref="BM6:BQ6"/>
     <mergeCell ref="AC6:AC8"/>
@@ -15102,72 +15177,6 @@
     <mergeCell ref="BD7:BD8"/>
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BK10 BM10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="19" priority="54"/>
@@ -15395,88 +15404,88 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="462"/>
-      <c r="B3" s="461"/>
-      <c r="C3" s="461"/>
-      <c r="D3" s="461"/>
-      <c r="E3" s="461"/>
-      <c r="F3" s="461"/>
-      <c r="G3" s="461"/>
-      <c r="H3" s="461"/>
-      <c r="I3" s="461"/>
-      <c r="J3" s="461"/>
-      <c r="K3" s="461"/>
-      <c r="L3" s="461"/>
-      <c r="M3" s="461"/>
-      <c r="N3" s="461"/>
-      <c r="O3" s="461"/>
-      <c r="P3" s="461"/>
-      <c r="Q3" s="461"/>
-      <c r="R3" s="461"/>
-      <c r="S3" s="461"/>
-      <c r="T3" s="461"/>
-      <c r="U3" s="461"/>
-      <c r="V3" s="461"/>
-      <c r="W3" s="461"/>
-      <c r="X3" s="461"/>
-      <c r="Y3" s="461"/>
-      <c r="Z3" s="461"/>
-      <c r="AA3" s="461"/>
-      <c r="AB3" s="461"/>
-      <c r="AC3" s="461"/>
-      <c r="AD3" s="461"/>
-      <c r="AE3" s="461"/>
-      <c r="AF3" s="461"/>
-      <c r="AG3" s="461"/>
-      <c r="AH3" s="461"/>
-      <c r="AI3" s="461"/>
-      <c r="AJ3" s="461"/>
-      <c r="AK3" s="461"/>
-      <c r="AL3" s="461"/>
-      <c r="AM3" s="461"/>
-      <c r="AN3" s="461"/>
-      <c r="AO3" s="461"/>
-      <c r="AP3" s="461"/>
-      <c r="AQ3" s="461"/>
-      <c r="AR3" s="461"/>
-      <c r="AS3" s="461"/>
-      <c r="AT3" s="461"/>
-      <c r="AU3" s="461"/>
-      <c r="AV3" s="461"/>
-      <c r="AW3" s="461"/>
-      <c r="AX3" s="461"/>
-      <c r="AY3" s="461"/>
-      <c r="AZ3" s="461"/>
-      <c r="BA3" s="461"/>
-      <c r="BB3" s="461"/>
-      <c r="BC3" s="461"/>
-      <c r="BD3" s="461"/>
-      <c r="BE3" s="461"/>
-      <c r="BF3" s="461"/>
-      <c r="BG3" s="461"/>
-      <c r="BH3" s="461"/>
-      <c r="BI3" s="461"/>
-      <c r="BJ3" s="461"/>
-      <c r="BK3" s="461"/>
-      <c r="BL3" s="461"/>
-      <c r="BM3" s="461"/>
-      <c r="BN3" s="461"/>
-      <c r="BO3" s="461"/>
-      <c r="BP3" s="461"/>
-      <c r="BQ3" s="461"/>
-      <c r="BR3" s="461"/>
-      <c r="BS3" s="461"/>
-      <c r="BT3" s="461"/>
-      <c r="BU3" s="461"/>
+      <c r="A3" s="469"/>
+      <c r="B3" s="468"/>
+      <c r="C3" s="468"/>
+      <c r="D3" s="468"/>
+      <c r="E3" s="468"/>
+      <c r="F3" s="468"/>
+      <c r="G3" s="468"/>
+      <c r="H3" s="468"/>
+      <c r="I3" s="468"/>
+      <c r="J3" s="468"/>
+      <c r="K3" s="468"/>
+      <c r="L3" s="468"/>
+      <c r="M3" s="468"/>
+      <c r="N3" s="468"/>
+      <c r="O3" s="468"/>
+      <c r="P3" s="468"/>
+      <c r="Q3" s="468"/>
+      <c r="R3" s="468"/>
+      <c r="S3" s="468"/>
+      <c r="T3" s="468"/>
+      <c r="U3" s="468"/>
+      <c r="V3" s="468"/>
+      <c r="W3" s="468"/>
+      <c r="X3" s="468"/>
+      <c r="Y3" s="468"/>
+      <c r="Z3" s="468"/>
+      <c r="AA3" s="468"/>
+      <c r="AB3" s="468"/>
+      <c r="AC3" s="468"/>
+      <c r="AD3" s="468"/>
+      <c r="AE3" s="468"/>
+      <c r="AF3" s="468"/>
+      <c r="AG3" s="468"/>
+      <c r="AH3" s="468"/>
+      <c r="AI3" s="468"/>
+      <c r="AJ3" s="468"/>
+      <c r="AK3" s="468"/>
+      <c r="AL3" s="468"/>
+      <c r="AM3" s="468"/>
+      <c r="AN3" s="468"/>
+      <c r="AO3" s="468"/>
+      <c r="AP3" s="468"/>
+      <c r="AQ3" s="468"/>
+      <c r="AR3" s="468"/>
+      <c r="AS3" s="468"/>
+      <c r="AT3" s="468"/>
+      <c r="AU3" s="468"/>
+      <c r="AV3" s="468"/>
+      <c r="AW3" s="468"/>
+      <c r="AX3" s="468"/>
+      <c r="AY3" s="468"/>
+      <c r="AZ3" s="468"/>
+      <c r="BA3" s="468"/>
+      <c r="BB3" s="468"/>
+      <c r="BC3" s="468"/>
+      <c r="BD3" s="468"/>
+      <c r="BE3" s="468"/>
+      <c r="BF3" s="468"/>
+      <c r="BG3" s="468"/>
+      <c r="BH3" s="468"/>
+      <c r="BI3" s="468"/>
+      <c r="BJ3" s="468"/>
+      <c r="BK3" s="468"/>
+      <c r="BL3" s="468"/>
+      <c r="BM3" s="468"/>
+      <c r="BN3" s="468"/>
+      <c r="BO3" s="468"/>
+      <c r="BP3" s="468"/>
+      <c r="BQ3" s="468"/>
+      <c r="BR3" s="468"/>
+      <c r="BS3" s="468"/>
+      <c r="BT3" s="468"/>
+      <c r="BU3" s="468"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="460" t="s">
+      <c r="BW3" s="467" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="461"/>
-      <c r="BY3" s="461"/>
-      <c r="BZ3" s="461"/>
-      <c r="CA3" s="461"/>
-      <c r="CB3" s="461"/>
+      <c r="BX3" s="468"/>
+      <c r="BY3" s="468"/>
+      <c r="BZ3" s="468"/>
+      <c r="CA3" s="468"/>
+      <c r="CB3" s="468"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -15560,12 +15569,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="461"/>
-      <c r="BX4" s="461"/>
-      <c r="BY4" s="461"/>
-      <c r="BZ4" s="461"/>
-      <c r="CA4" s="461"/>
-      <c r="CB4" s="461"/>
+      <c r="BW4" s="468"/>
+      <c r="BX4" s="468"/>
+      <c r="BY4" s="468"/>
+      <c r="BZ4" s="468"/>
+      <c r="CA4" s="468"/>
+      <c r="CB4" s="468"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -15643,12 +15652,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="389"/>
-      <c r="BX5" s="389"/>
-      <c r="BY5" s="389"/>
-      <c r="BZ5" s="389"/>
-      <c r="CA5" s="389"/>
-      <c r="CB5" s="389"/>
+      <c r="BW5" s="361"/>
+      <c r="BX5" s="361"/>
+      <c r="BY5" s="361"/>
+      <c r="BZ5" s="361"/>
+      <c r="CA5" s="361"/>
+      <c r="CB5" s="361"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15726,12 +15735,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="389"/>
-      <c r="BX6" s="389"/>
-      <c r="BY6" s="389"/>
-      <c r="BZ6" s="389"/>
-      <c r="CA6" s="389"/>
-      <c r="CB6" s="389"/>
+      <c r="BW6" s="361"/>
+      <c r="BX6" s="361"/>
+      <c r="BY6" s="361"/>
+      <c r="BZ6" s="361"/>
+      <c r="CA6" s="361"/>
+      <c r="CB6" s="361"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15819,358 +15828,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="472" t="s">
+      <c r="A8" s="452" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="464" t="s">
+      <c r="B8" s="470" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="476" t="s">
+      <c r="C8" s="456" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="450" t="s">
+      <c r="D8" s="459" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="450" t="s">
+      <c r="E8" s="459" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="468" t="s">
+      <c r="F8" s="463" t="s">
         <v>142</v>
       </c>
-      <c r="G8" s="453" t="s">
+      <c r="G8" s="474" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="373" t="s">
+      <c r="H8" s="389" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="373" t="s">
+      <c r="I8" s="389" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="453" t="s">
+      <c r="J8" s="474" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="471" t="s">
+      <c r="K8" s="466" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="425"/>
-      <c r="M8" s="425"/>
-      <c r="N8" s="425"/>
-      <c r="O8" s="425"/>
-      <c r="P8" s="425"/>
-      <c r="Q8" s="425"/>
-      <c r="R8" s="425"/>
-      <c r="S8" s="425"/>
-      <c r="T8" s="425"/>
-      <c r="U8" s="425"/>
-      <c r="V8" s="425"/>
-      <c r="W8" s="425"/>
-      <c r="X8" s="425"/>
-      <c r="Y8" s="448" t="s">
+      <c r="L8" s="413"/>
+      <c r="M8" s="413"/>
+      <c r="N8" s="413"/>
+      <c r="O8" s="413"/>
+      <c r="P8" s="413"/>
+      <c r="Q8" s="413"/>
+      <c r="R8" s="413"/>
+      <c r="S8" s="413"/>
+      <c r="T8" s="413"/>
+      <c r="U8" s="413"/>
+      <c r="V8" s="413"/>
+      <c r="W8" s="413"/>
+      <c r="X8" s="413"/>
+      <c r="Y8" s="451" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="425"/>
-      <c r="AA8" s="425"/>
-      <c r="AB8" s="425"/>
-      <c r="AC8" s="425"/>
-      <c r="AD8" s="425"/>
-      <c r="AE8" s="425"/>
-      <c r="AF8" s="425"/>
-      <c r="AG8" s="425"/>
-      <c r="AH8" s="425"/>
-      <c r="AI8" s="425"/>
-      <c r="AJ8" s="425"/>
-      <c r="AK8" s="425"/>
-      <c r="AL8" s="425"/>
-      <c r="AM8" s="425"/>
-      <c r="AN8" s="425"/>
-      <c r="AO8" s="426"/>
-      <c r="AP8" s="448" t="s">
+      <c r="Z8" s="413"/>
+      <c r="AA8" s="413"/>
+      <c r="AB8" s="413"/>
+      <c r="AC8" s="413"/>
+      <c r="AD8" s="413"/>
+      <c r="AE8" s="413"/>
+      <c r="AF8" s="413"/>
+      <c r="AG8" s="413"/>
+      <c r="AH8" s="413"/>
+      <c r="AI8" s="413"/>
+      <c r="AJ8" s="413"/>
+      <c r="AK8" s="413"/>
+      <c r="AL8" s="413"/>
+      <c r="AM8" s="413"/>
+      <c r="AN8" s="413"/>
+      <c r="AO8" s="414"/>
+      <c r="AP8" s="451" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="448" t="s">
+      <c r="AQ8" s="451" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="448" t="s">
+      <c r="AR8" s="451" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="448" t="s">
+      <c r="AS8" s="451" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="448" t="s">
+      <c r="AT8" s="451" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="448" t="s">
+      <c r="AU8" s="451" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="413" t="s">
+      <c r="AV8" s="417" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="413" t="s">
+      <c r="AW8" s="417" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="413" t="s">
+      <c r="AX8" s="417" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="424" t="s">
+      <c r="AY8" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="425"/>
-      <c r="BA8" s="425"/>
-      <c r="BB8" s="425"/>
-      <c r="BC8" s="425"/>
-      <c r="BD8" s="425"/>
-      <c r="BE8" s="425"/>
-      <c r="BF8" s="425"/>
-      <c r="BG8" s="425"/>
-      <c r="BH8" s="425"/>
-      <c r="BI8" s="425"/>
-      <c r="BJ8" s="425"/>
-      <c r="BK8" s="425"/>
-      <c r="BL8" s="425"/>
-      <c r="BM8" s="425"/>
-      <c r="BN8" s="425"/>
-      <c r="BO8" s="425"/>
-      <c r="BP8" s="426"/>
-      <c r="BQ8" s="430" t="s">
+      <c r="AZ8" s="413"/>
+      <c r="BA8" s="413"/>
+      <c r="BB8" s="413"/>
+      <c r="BC8" s="413"/>
+      <c r="BD8" s="413"/>
+      <c r="BE8" s="413"/>
+      <c r="BF8" s="413"/>
+      <c r="BG8" s="413"/>
+      <c r="BH8" s="413"/>
+      <c r="BI8" s="413"/>
+      <c r="BJ8" s="413"/>
+      <c r="BK8" s="413"/>
+      <c r="BL8" s="413"/>
+      <c r="BM8" s="413"/>
+      <c r="BN8" s="413"/>
+      <c r="BO8" s="413"/>
+      <c r="BP8" s="414"/>
+      <c r="BQ8" s="433" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="431"/>
-      <c r="BS8" s="424" t="s">
+      <c r="BR8" s="427"/>
+      <c r="BS8" s="412" t="s">
         <v>143</v>
       </c>
-      <c r="BT8" s="424" t="s">
+      <c r="BT8" s="412" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="418" t="s">
+      <c r="BU8" s="444" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="421" t="s">
+      <c r="BW8" s="445" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="432" t="s">
+      <c r="BX8" s="434" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="433"/>
-      <c r="BZ8" s="433"/>
-      <c r="CA8" s="431"/>
-      <c r="CB8" s="427" t="s">
+      <c r="BY8" s="435"/>
+      <c r="BZ8" s="435"/>
+      <c r="CA8" s="427"/>
+      <c r="CB8" s="446" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="333" t="s">
+      <c r="CC8" s="362" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="333" t="s">
+      <c r="CD8" s="362" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="473"/>
-      <c r="B9" s="465"/>
-      <c r="C9" s="477"/>
-      <c r="D9" s="451"/>
-      <c r="E9" s="451"/>
-      <c r="F9" s="469"/>
-      <c r="G9" s="454"/>
-      <c r="H9" s="374"/>
-      <c r="I9" s="374"/>
-      <c r="J9" s="454"/>
-      <c r="K9" s="456" t="s">
+      <c r="A9" s="453"/>
+      <c r="B9" s="471"/>
+      <c r="C9" s="457"/>
+      <c r="D9" s="460"/>
+      <c r="E9" s="460"/>
+      <c r="F9" s="464"/>
+      <c r="G9" s="475"/>
+      <c r="H9" s="390"/>
+      <c r="I9" s="390"/>
+      <c r="J9" s="475"/>
+      <c r="K9" s="447" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="456" t="s">
+      <c r="L9" s="447" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="456" t="s">
+      <c r="M9" s="447" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="456" t="s">
+      <c r="N9" s="447" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="456" t="s">
+      <c r="O9" s="447" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="456" t="s">
+      <c r="P9" s="447" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="456" t="s">
+      <c r="Q9" s="447" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="456" t="s">
+      <c r="R9" s="447" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="456" t="s">
+      <c r="S9" s="447" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="456" t="s">
+      <c r="T9" s="447" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="456" t="s">
+      <c r="U9" s="447" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="459" t="s">
+      <c r="V9" s="477" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="431"/>
-      <c r="X9" s="456" t="s">
+      <c r="W9" s="427"/>
+      <c r="X9" s="447" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="447" t="s">
+      <c r="Y9" s="449" t="s">
         <v>154</v>
       </c>
-      <c r="Z9" s="447" t="s">
+      <c r="Z9" s="449" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="447" t="s">
+      <c r="AA9" s="449" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="447" t="s">
+      <c r="AB9" s="449" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="463" t="s">
+      <c r="AC9" s="450" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="463" t="s">
+      <c r="AD9" s="450" t="s">
         <v>144</v>
       </c>
-      <c r="AE9" s="463" t="s">
+      <c r="AE9" s="450" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="463" t="s">
+      <c r="AF9" s="450" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="447" t="s">
+      <c r="AG9" s="449" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="463" t="s">
+      <c r="AH9" s="450" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="463" t="s">
+      <c r="AI9" s="450" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="447" t="s">
+      <c r="AJ9" s="449" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="442" t="s">
+      <c r="AK9" s="419" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="413" t="s">
+      <c r="AL9" s="417" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="447" t="s">
+      <c r="AM9" s="449" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="444" t="s">
+      <c r="AN9" s="423" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="413" t="s">
+      <c r="AO9" s="417" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="409"/>
-      <c r="AQ9" s="409"/>
-      <c r="AR9" s="409"/>
-      <c r="AS9" s="409"/>
-      <c r="AT9" s="409"/>
-      <c r="AU9" s="409"/>
-      <c r="AV9" s="409"/>
-      <c r="AW9" s="409"/>
-      <c r="AX9" s="409"/>
-      <c r="AY9" s="424" t="s">
+      <c r="AP9" s="410"/>
+      <c r="AQ9" s="410"/>
+      <c r="AR9" s="410"/>
+      <c r="AS9" s="410"/>
+      <c r="AT9" s="410"/>
+      <c r="AU9" s="410"/>
+      <c r="AV9" s="410"/>
+      <c r="AW9" s="410"/>
+      <c r="AX9" s="410"/>
+      <c r="AY9" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="AZ9" s="425"/>
-      <c r="BA9" s="425"/>
-      <c r="BB9" s="425"/>
-      <c r="BC9" s="425"/>
-      <c r="BD9" s="425"/>
-      <c r="BE9" s="425"/>
-      <c r="BF9" s="425"/>
-      <c r="BG9" s="425"/>
-      <c r="BH9" s="425"/>
-      <c r="BI9" s="425"/>
-      <c r="BJ9" s="426"/>
-      <c r="BK9" s="424" t="s">
+      <c r="AZ9" s="413"/>
+      <c r="BA9" s="413"/>
+      <c r="BB9" s="413"/>
+      <c r="BC9" s="413"/>
+      <c r="BD9" s="413"/>
+      <c r="BE9" s="413"/>
+      <c r="BF9" s="413"/>
+      <c r="BG9" s="413"/>
+      <c r="BH9" s="413"/>
+      <c r="BI9" s="413"/>
+      <c r="BJ9" s="414"/>
+      <c r="BK9" s="412" t="s">
         <v>64</v>
       </c>
-      <c r="BL9" s="425"/>
-      <c r="BM9" s="425"/>
-      <c r="BN9" s="425"/>
-      <c r="BO9" s="425"/>
-      <c r="BP9" s="426"/>
-      <c r="BQ9" s="411" t="s">
+      <c r="BL9" s="413"/>
+      <c r="BM9" s="413"/>
+      <c r="BN9" s="413"/>
+      <c r="BO9" s="413"/>
+      <c r="BP9" s="414"/>
+      <c r="BQ9" s="409" t="s">
         <v>65</v>
       </c>
-      <c r="BR9" s="411" t="s">
+      <c r="BR9" s="409" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="409"/>
-      <c r="BT9" s="409"/>
-      <c r="BU9" s="419"/>
+      <c r="BS9" s="410"/>
+      <c r="BT9" s="410"/>
+      <c r="BU9" s="420"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="422"/>
-      <c r="BX9" s="419"/>
-      <c r="BY9" s="475"/>
-      <c r="BZ9" s="475"/>
-      <c r="CA9" s="422"/>
-      <c r="CB9" s="409"/>
-      <c r="CC9" s="409"/>
-      <c r="CD9" s="409"/>
+      <c r="BW9" s="437"/>
+      <c r="BX9" s="420"/>
+      <c r="BY9" s="455"/>
+      <c r="BZ9" s="455"/>
+      <c r="CA9" s="437"/>
+      <c r="CB9" s="410"/>
+      <c r="CC9" s="410"/>
+      <c r="CD9" s="410"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="473"/>
-      <c r="B10" s="465"/>
-      <c r="C10" s="477"/>
-      <c r="D10" s="451"/>
-      <c r="E10" s="451"/>
-      <c r="F10" s="469"/>
-      <c r="G10" s="454"/>
-      <c r="H10" s="374"/>
-      <c r="I10" s="374"/>
-      <c r="J10" s="454"/>
-      <c r="K10" s="409"/>
-      <c r="L10" s="409"/>
-      <c r="M10" s="409"/>
-      <c r="N10" s="409"/>
-      <c r="O10" s="409"/>
-      <c r="P10" s="409"/>
-      <c r="Q10" s="409"/>
-      <c r="R10" s="409"/>
-      <c r="S10" s="409"/>
-      <c r="T10" s="409"/>
-      <c r="U10" s="409"/>
-      <c r="V10" s="420"/>
-      <c r="W10" s="446"/>
-      <c r="X10" s="409"/>
-      <c r="Y10" s="409"/>
-      <c r="Z10" s="409"/>
-      <c r="AA10" s="409"/>
-      <c r="AB10" s="409"/>
-      <c r="AC10" s="409"/>
-      <c r="AD10" s="409"/>
-      <c r="AE10" s="409"/>
-      <c r="AF10" s="409"/>
-      <c r="AG10" s="409"/>
-      <c r="AH10" s="409"/>
-      <c r="AI10" s="409"/>
-      <c r="AJ10" s="409"/>
-      <c r="AK10" s="419"/>
-      <c r="AL10" s="409"/>
-      <c r="AM10" s="409"/>
-      <c r="AN10" s="409"/>
-      <c r="AO10" s="409"/>
-      <c r="AP10" s="409"/>
-      <c r="AQ10" s="409"/>
-      <c r="AR10" s="409"/>
-      <c r="AS10" s="409"/>
-      <c r="AT10" s="409"/>
-      <c r="AU10" s="409"/>
-      <c r="AV10" s="409"/>
-      <c r="AW10" s="409"/>
-      <c r="AX10" s="409"/>
+      <c r="A10" s="453"/>
+      <c r="B10" s="471"/>
+      <c r="C10" s="457"/>
+      <c r="D10" s="460"/>
+      <c r="E10" s="460"/>
+      <c r="F10" s="464"/>
+      <c r="G10" s="475"/>
+      <c r="H10" s="390"/>
+      <c r="I10" s="390"/>
+      <c r="J10" s="475"/>
+      <c r="K10" s="410"/>
+      <c r="L10" s="410"/>
+      <c r="M10" s="410"/>
+      <c r="N10" s="410"/>
+      <c r="O10" s="410"/>
+      <c r="P10" s="410"/>
+      <c r="Q10" s="410"/>
+      <c r="R10" s="410"/>
+      <c r="S10" s="410"/>
+      <c r="T10" s="410"/>
+      <c r="U10" s="410"/>
+      <c r="V10" s="421"/>
+      <c r="W10" s="428"/>
+      <c r="X10" s="410"/>
+      <c r="Y10" s="410"/>
+      <c r="Z10" s="410"/>
+      <c r="AA10" s="410"/>
+      <c r="AB10" s="410"/>
+      <c r="AC10" s="410"/>
+      <c r="AD10" s="410"/>
+      <c r="AE10" s="410"/>
+      <c r="AF10" s="410"/>
+      <c r="AG10" s="410"/>
+      <c r="AH10" s="410"/>
+      <c r="AI10" s="410"/>
+      <c r="AJ10" s="410"/>
+      <c r="AK10" s="420"/>
+      <c r="AL10" s="410"/>
+      <c r="AM10" s="410"/>
+      <c r="AN10" s="410"/>
+      <c r="AO10" s="410"/>
+      <c r="AP10" s="410"/>
+      <c r="AQ10" s="410"/>
+      <c r="AR10" s="410"/>
+      <c r="AS10" s="410"/>
+      <c r="AT10" s="410"/>
+      <c r="AU10" s="410"/>
+      <c r="AV10" s="410"/>
+      <c r="AW10" s="410"/>
+      <c r="AX10" s="410"/>
       <c r="AY10" s="101" t="s">
         <v>67</v>
       </c>
@@ -16180,123 +16189,123 @@
       <c r="BA10" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB10" s="467" t="s">
+      <c r="BB10" s="473" t="s">
         <v>70</v>
       </c>
-      <c r="BC10" s="457" t="s">
+      <c r="BC10" s="448" t="s">
         <v>71</v>
       </c>
-      <c r="BD10" s="457" t="s">
+      <c r="BD10" s="448" t="s">
         <v>72</v>
       </c>
-      <c r="BE10" s="457" t="s">
+      <c r="BE10" s="448" t="s">
         <v>145</v>
       </c>
-      <c r="BF10" s="457" t="s">
+      <c r="BF10" s="448" t="s">
         <v>74</v>
       </c>
-      <c r="BG10" s="457" t="s">
+      <c r="BG10" s="448" t="s">
         <v>75</v>
       </c>
-      <c r="BH10" s="457" t="s">
+      <c r="BH10" s="448" t="s">
         <v>76</v>
       </c>
-      <c r="BI10" s="457" t="s">
+      <c r="BI10" s="448" t="s">
         <v>79</v>
       </c>
-      <c r="BJ10" s="449" t="s">
+      <c r="BJ10" s="478" t="s">
         <v>80</v>
       </c>
-      <c r="BK10" s="457" t="s">
+      <c r="BK10" s="448" t="s">
         <v>81</v>
       </c>
-      <c r="BL10" s="458" t="s">
+      <c r="BL10" s="462" t="s">
         <v>82</v>
       </c>
-      <c r="BM10" s="457" t="s">
+      <c r="BM10" s="448" t="s">
         <v>83</v>
       </c>
-      <c r="BN10" s="458" t="s">
+      <c r="BN10" s="462" t="s">
         <v>84</v>
       </c>
-      <c r="BO10" s="458" t="s">
+      <c r="BO10" s="462" t="s">
         <v>146</v>
       </c>
-      <c r="BP10" s="424" t="s">
+      <c r="BP10" s="412" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="409"/>
-      <c r="BR10" s="409"/>
-      <c r="BS10" s="409"/>
-      <c r="BT10" s="409"/>
-      <c r="BU10" s="419"/>
+      <c r="BQ10" s="410"/>
+      <c r="BR10" s="410"/>
+      <c r="BS10" s="410"/>
+      <c r="BT10" s="410"/>
+      <c r="BU10" s="420"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="422"/>
-      <c r="BX10" s="435"/>
-      <c r="BY10" s="436"/>
-      <c r="BZ10" s="436"/>
-      <c r="CA10" s="423"/>
-      <c r="CB10" s="409"/>
-      <c r="CC10" s="409"/>
-      <c r="CD10" s="409"/>
+      <c r="BW10" s="437"/>
+      <c r="BX10" s="438"/>
+      <c r="BY10" s="439"/>
+      <c r="BZ10" s="439"/>
+      <c r="CA10" s="440"/>
+      <c r="CB10" s="410"/>
+      <c r="CC10" s="410"/>
+      <c r="CD10" s="410"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A11" s="474"/>
-      <c r="B11" s="466"/>
-      <c r="C11" s="478"/>
-      <c r="D11" s="452"/>
-      <c r="E11" s="452"/>
-      <c r="F11" s="470"/>
-      <c r="G11" s="455"/>
-      <c r="H11" s="375"/>
-      <c r="I11" s="375"/>
-      <c r="J11" s="455"/>
-      <c r="K11" s="412"/>
-      <c r="L11" s="412"/>
-      <c r="M11" s="412"/>
-      <c r="N11" s="412"/>
-      <c r="O11" s="412"/>
-      <c r="P11" s="412"/>
-      <c r="Q11" s="412"/>
-      <c r="R11" s="412"/>
-      <c r="S11" s="412"/>
-      <c r="T11" s="412"/>
-      <c r="U11" s="412"/>
+      <c r="A11" s="454"/>
+      <c r="B11" s="472"/>
+      <c r="C11" s="458"/>
+      <c r="D11" s="461"/>
+      <c r="E11" s="461"/>
+      <c r="F11" s="465"/>
+      <c r="G11" s="476"/>
+      <c r="H11" s="391"/>
+      <c r="I11" s="391"/>
+      <c r="J11" s="476"/>
+      <c r="K11" s="411"/>
+      <c r="L11" s="411"/>
+      <c r="M11" s="411"/>
+      <c r="N11" s="411"/>
+      <c r="O11" s="411"/>
+      <c r="P11" s="411"/>
+      <c r="Q11" s="411"/>
+      <c r="R11" s="411"/>
+      <c r="S11" s="411"/>
+      <c r="T11" s="411"/>
+      <c r="U11" s="411"/>
       <c r="V11" s="30" t="s">
         <v>86</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="X11" s="412"/>
-      <c r="Y11" s="412"/>
-      <c r="Z11" s="412"/>
-      <c r="AA11" s="412"/>
-      <c r="AB11" s="412"/>
-      <c r="AC11" s="412"/>
-      <c r="AD11" s="412"/>
-      <c r="AE11" s="412"/>
-      <c r="AF11" s="412"/>
-      <c r="AG11" s="412"/>
-      <c r="AH11" s="412"/>
-      <c r="AI11" s="412"/>
-      <c r="AJ11" s="412"/>
-      <c r="AK11" s="420"/>
-      <c r="AL11" s="412"/>
-      <c r="AM11" s="412"/>
-      <c r="AN11" s="412"/>
-      <c r="AO11" s="412"/>
-      <c r="AP11" s="412"/>
-      <c r="AQ11" s="412"/>
-      <c r="AR11" s="412"/>
-      <c r="AS11" s="412"/>
-      <c r="AT11" s="412"/>
-      <c r="AU11" s="412"/>
-      <c r="AV11" s="412"/>
-      <c r="AW11" s="412"/>
-      <c r="AX11" s="412"/>
+      <c r="X11" s="411"/>
+      <c r="Y11" s="411"/>
+      <c r="Z11" s="411"/>
+      <c r="AA11" s="411"/>
+      <c r="AB11" s="411"/>
+      <c r="AC11" s="411"/>
+      <c r="AD11" s="411"/>
+      <c r="AE11" s="411"/>
+      <c r="AF11" s="411"/>
+      <c r="AG11" s="411"/>
+      <c r="AH11" s="411"/>
+      <c r="AI11" s="411"/>
+      <c r="AJ11" s="411"/>
+      <c r="AK11" s="421"/>
+      <c r="AL11" s="411"/>
+      <c r="AM11" s="411"/>
+      <c r="AN11" s="411"/>
+      <c r="AO11" s="411"/>
+      <c r="AP11" s="411"/>
+      <c r="AQ11" s="411"/>
+      <c r="AR11" s="411"/>
+      <c r="AS11" s="411"/>
+      <c r="AT11" s="411"/>
+      <c r="AU11" s="411"/>
+      <c r="AV11" s="411"/>
+      <c r="AW11" s="411"/>
+      <c r="AX11" s="411"/>
       <c r="AY11" s="102" t="s">
         <v>88</v>
       </c>
@@ -16306,28 +16315,28 @@
       <c r="BA11" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB11" s="412"/>
-      <c r="BC11" s="412"/>
-      <c r="BD11" s="412"/>
-      <c r="BE11" s="412"/>
-      <c r="BF11" s="412"/>
-      <c r="BG11" s="412"/>
-      <c r="BH11" s="412"/>
-      <c r="BI11" s="412"/>
-      <c r="BJ11" s="412"/>
-      <c r="BK11" s="412"/>
-      <c r="BL11" s="412"/>
-      <c r="BM11" s="412"/>
-      <c r="BN11" s="412"/>
-      <c r="BO11" s="412"/>
-      <c r="BP11" s="412"/>
-      <c r="BQ11" s="412"/>
-      <c r="BR11" s="412"/>
-      <c r="BS11" s="412"/>
-      <c r="BT11" s="412"/>
-      <c r="BU11" s="420"/>
+      <c r="BB11" s="411"/>
+      <c r="BC11" s="411"/>
+      <c r="BD11" s="411"/>
+      <c r="BE11" s="411"/>
+      <c r="BF11" s="411"/>
+      <c r="BG11" s="411"/>
+      <c r="BH11" s="411"/>
+      <c r="BI11" s="411"/>
+      <c r="BJ11" s="411"/>
+      <c r="BK11" s="411"/>
+      <c r="BL11" s="411"/>
+      <c r="BM11" s="411"/>
+      <c r="BN11" s="411"/>
+      <c r="BO11" s="411"/>
+      <c r="BP11" s="411"/>
+      <c r="BQ11" s="411"/>
+      <c r="BR11" s="411"/>
+      <c r="BS11" s="411"/>
+      <c r="BT11" s="411"/>
+      <c r="BU11" s="421"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="423"/>
+      <c r="BW11" s="440"/>
       <c r="BX11" s="72" t="s">
         <v>91</v>
       </c>
@@ -16340,9 +16349,9 @@
       <c r="CA11" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB11" s="410"/>
-      <c r="CC11" s="410"/>
-      <c r="CD11" s="410"/>
+      <c r="CB11" s="432"/>
+      <c r="CC11" s="432"/>
+      <c r="CD11" s="432"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18743,16 +18752,62 @@
   </sheetData>
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AY8:BP8"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="AH9:AH11"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="BX8:CA10"/>
@@ -18769,62 +18824,16 @@
     <mergeCell ref="AC9:AC11"/>
     <mergeCell ref="AP8:AP11"/>
     <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="T9:T11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AY8:BP8"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AV8:AV11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 B22:B1048576 C12:BU12">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -19054,87 +19063,87 @@
       <c r="CD2" s="132"/>
     </row>
     <row r="3" spans="1:87" s="134" customFormat="1" ht="11" outlineLevel="1">
-      <c r="A3" s="438"/>
-      <c r="B3" s="429"/>
-      <c r="C3" s="429"/>
-      <c r="D3" s="429"/>
-      <c r="E3" s="429"/>
-      <c r="F3" s="429"/>
-      <c r="G3" s="429"/>
-      <c r="H3" s="429"/>
-      <c r="I3" s="429"/>
-      <c r="J3" s="429"/>
-      <c r="K3" s="429"/>
-      <c r="L3" s="429"/>
-      <c r="M3" s="429"/>
-      <c r="N3" s="429"/>
-      <c r="O3" s="429"/>
-      <c r="P3" s="429"/>
-      <c r="Q3" s="429"/>
-      <c r="R3" s="429"/>
-      <c r="S3" s="429"/>
-      <c r="T3" s="429"/>
-      <c r="U3" s="429"/>
-      <c r="V3" s="429"/>
-      <c r="W3" s="429"/>
-      <c r="X3" s="429"/>
-      <c r="Y3" s="429"/>
-      <c r="Z3" s="429"/>
-      <c r="AA3" s="429"/>
-      <c r="AB3" s="429"/>
-      <c r="AC3" s="429"/>
-      <c r="AD3" s="429"/>
-      <c r="AE3" s="429"/>
-      <c r="AF3" s="429"/>
-      <c r="AG3" s="429"/>
-      <c r="AH3" s="429"/>
-      <c r="AI3" s="429"/>
-      <c r="AJ3" s="429"/>
-      <c r="AK3" s="429"/>
-      <c r="AL3" s="429"/>
-      <c r="AM3" s="429"/>
-      <c r="AN3" s="429"/>
-      <c r="AO3" s="429"/>
-      <c r="AP3" s="429"/>
-      <c r="AQ3" s="429"/>
-      <c r="AR3" s="429"/>
-      <c r="AS3" s="429"/>
-      <c r="AT3" s="429"/>
-      <c r="AU3" s="429"/>
-      <c r="AV3" s="429"/>
-      <c r="AW3" s="429"/>
-      <c r="AX3" s="429"/>
-      <c r="AY3" s="429"/>
-      <c r="AZ3" s="429"/>
-      <c r="BA3" s="429"/>
-      <c r="BB3" s="429"/>
-      <c r="BC3" s="429"/>
-      <c r="BD3" s="429"/>
-      <c r="BE3" s="429"/>
-      <c r="BF3" s="429"/>
-      <c r="BG3" s="429"/>
-      <c r="BH3" s="429"/>
-      <c r="BI3" s="429"/>
-      <c r="BJ3" s="429"/>
-      <c r="BK3" s="429"/>
-      <c r="BL3" s="429"/>
-      <c r="BM3" s="429"/>
-      <c r="BN3" s="429"/>
-      <c r="BO3" s="429"/>
-      <c r="BP3" s="429"/>
-      <c r="BQ3" s="429"/>
-      <c r="BR3" s="429"/>
-      <c r="BS3" s="429"/>
-      <c r="BT3" s="429"/>
-      <c r="BU3" s="429"/>
-      <c r="BW3" s="428" t="s">
+      <c r="A3" s="442"/>
+      <c r="B3" s="431"/>
+      <c r="C3" s="431"/>
+      <c r="D3" s="431"/>
+      <c r="E3" s="431"/>
+      <c r="F3" s="431"/>
+      <c r="G3" s="431"/>
+      <c r="H3" s="431"/>
+      <c r="I3" s="431"/>
+      <c r="J3" s="431"/>
+      <c r="K3" s="431"/>
+      <c r="L3" s="431"/>
+      <c r="M3" s="431"/>
+      <c r="N3" s="431"/>
+      <c r="O3" s="431"/>
+      <c r="P3" s="431"/>
+      <c r="Q3" s="431"/>
+      <c r="R3" s="431"/>
+      <c r="S3" s="431"/>
+      <c r="T3" s="431"/>
+      <c r="U3" s="431"/>
+      <c r="V3" s="431"/>
+      <c r="W3" s="431"/>
+      <c r="X3" s="431"/>
+      <c r="Y3" s="431"/>
+      <c r="Z3" s="431"/>
+      <c r="AA3" s="431"/>
+      <c r="AB3" s="431"/>
+      <c r="AC3" s="431"/>
+      <c r="AD3" s="431"/>
+      <c r="AE3" s="431"/>
+      <c r="AF3" s="431"/>
+      <c r="AG3" s="431"/>
+      <c r="AH3" s="431"/>
+      <c r="AI3" s="431"/>
+      <c r="AJ3" s="431"/>
+      <c r="AK3" s="431"/>
+      <c r="AL3" s="431"/>
+      <c r="AM3" s="431"/>
+      <c r="AN3" s="431"/>
+      <c r="AO3" s="431"/>
+      <c r="AP3" s="431"/>
+      <c r="AQ3" s="431"/>
+      <c r="AR3" s="431"/>
+      <c r="AS3" s="431"/>
+      <c r="AT3" s="431"/>
+      <c r="AU3" s="431"/>
+      <c r="AV3" s="431"/>
+      <c r="AW3" s="431"/>
+      <c r="AX3" s="431"/>
+      <c r="AY3" s="431"/>
+      <c r="AZ3" s="431"/>
+      <c r="BA3" s="431"/>
+      <c r="BB3" s="431"/>
+      <c r="BC3" s="431"/>
+      <c r="BD3" s="431"/>
+      <c r="BE3" s="431"/>
+      <c r="BF3" s="431"/>
+      <c r="BG3" s="431"/>
+      <c r="BH3" s="431"/>
+      <c r="BI3" s="431"/>
+      <c r="BJ3" s="431"/>
+      <c r="BK3" s="431"/>
+      <c r="BL3" s="431"/>
+      <c r="BM3" s="431"/>
+      <c r="BN3" s="431"/>
+      <c r="BO3" s="431"/>
+      <c r="BP3" s="431"/>
+      <c r="BQ3" s="431"/>
+      <c r="BR3" s="431"/>
+      <c r="BS3" s="431"/>
+      <c r="BT3" s="431"/>
+      <c r="BU3" s="431"/>
+      <c r="BW3" s="430" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="429"/>
-      <c r="BY3" s="429"/>
-      <c r="BZ3" s="429"/>
-      <c r="CA3" s="429"/>
-      <c r="CB3" s="429"/>
+      <c r="BX3" s="431"/>
+      <c r="BY3" s="431"/>
+      <c r="BZ3" s="431"/>
+      <c r="CA3" s="431"/>
+      <c r="CB3" s="431"/>
       <c r="CC3" s="133"/>
       <c r="CD3" s="133"/>
       <c r="CE3" s="134" t="s">
@@ -19217,366 +19226,366 @@
       <c r="BS4" s="135"/>
       <c r="BT4" s="135"/>
       <c r="BU4" s="135"/>
-      <c r="BW4" s="429"/>
-      <c r="BX4" s="429"/>
-      <c r="BY4" s="429"/>
-      <c r="BZ4" s="429"/>
-      <c r="CA4" s="429"/>
-      <c r="CB4" s="429"/>
+      <c r="BW4" s="431"/>
+      <c r="BX4" s="431"/>
+      <c r="BY4" s="431"/>
+      <c r="BZ4" s="431"/>
+      <c r="CA4" s="431"/>
+      <c r="CB4" s="431"/>
       <c r="CC4" s="133"/>
       <c r="CD4" s="133"/>
     </row>
     <row r="5" spans="1:87" s="136" customFormat="1">
-      <c r="A5" s="441" t="s">
+      <c r="A5" s="418" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="440" t="s">
+      <c r="B5" s="429" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="413" t="s">
+      <c r="C5" s="417" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="439" t="s">
+      <c r="D5" s="424" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="439" t="s">
+      <c r="E5" s="424" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="479" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="413" t="s">
+      <c r="G5" s="417" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="417" t="s">
+      <c r="H5" s="415" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="417" t="s">
+      <c r="I5" s="415" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="413" t="s">
+      <c r="J5" s="417" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="443" t="s">
+      <c r="K5" s="422" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="425"/>
-      <c r="M5" s="425"/>
-      <c r="N5" s="425"/>
-      <c r="O5" s="425"/>
-      <c r="P5" s="425"/>
-      <c r="Q5" s="425"/>
-      <c r="R5" s="425"/>
-      <c r="S5" s="425"/>
-      <c r="T5" s="425"/>
-      <c r="U5" s="425"/>
-      <c r="V5" s="425"/>
-      <c r="W5" s="425"/>
-      <c r="X5" s="425"/>
-      <c r="Y5" s="413" t="s">
+      <c r="L5" s="413"/>
+      <c r="M5" s="413"/>
+      <c r="N5" s="413"/>
+      <c r="O5" s="413"/>
+      <c r="P5" s="413"/>
+      <c r="Q5" s="413"/>
+      <c r="R5" s="413"/>
+      <c r="S5" s="413"/>
+      <c r="T5" s="413"/>
+      <c r="U5" s="413"/>
+      <c r="V5" s="413"/>
+      <c r="W5" s="413"/>
+      <c r="X5" s="413"/>
+      <c r="Y5" s="417" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="425"/>
-      <c r="AA5" s="425"/>
-      <c r="AB5" s="425"/>
-      <c r="AC5" s="425"/>
-      <c r="AD5" s="425"/>
-      <c r="AE5" s="425"/>
-      <c r="AF5" s="425"/>
-      <c r="AG5" s="425"/>
-      <c r="AH5" s="425"/>
-      <c r="AI5" s="425"/>
-      <c r="AJ5" s="425"/>
-      <c r="AK5" s="425"/>
-      <c r="AL5" s="425"/>
-      <c r="AM5" s="425"/>
-      <c r="AN5" s="425"/>
-      <c r="AO5" s="426"/>
-      <c r="AP5" s="413" t="s">
+      <c r="Z5" s="413"/>
+      <c r="AA5" s="413"/>
+      <c r="AB5" s="413"/>
+      <c r="AC5" s="413"/>
+      <c r="AD5" s="413"/>
+      <c r="AE5" s="413"/>
+      <c r="AF5" s="413"/>
+      <c r="AG5" s="413"/>
+      <c r="AH5" s="413"/>
+      <c r="AI5" s="413"/>
+      <c r="AJ5" s="413"/>
+      <c r="AK5" s="413"/>
+      <c r="AL5" s="413"/>
+      <c r="AM5" s="413"/>
+      <c r="AN5" s="413"/>
+      <c r="AO5" s="414"/>
+      <c r="AP5" s="417" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="413" t="s">
+      <c r="AQ5" s="417" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="413" t="s">
+      <c r="AR5" s="417" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="413" t="s">
+      <c r="AS5" s="417" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="413" t="s">
+      <c r="AT5" s="417" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="413" t="s">
+      <c r="AU5" s="417" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="413" t="s">
+      <c r="AV5" s="417" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="413" t="s">
+      <c r="AW5" s="417" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="413" t="s">
+      <c r="AX5" s="417" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="424" t="s">
+      <c r="AY5" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="425"/>
-      <c r="BA5" s="425"/>
-      <c r="BB5" s="425"/>
-      <c r="BC5" s="425"/>
-      <c r="BD5" s="425"/>
-      <c r="BE5" s="425"/>
-      <c r="BF5" s="425"/>
-      <c r="BG5" s="425"/>
-      <c r="BH5" s="425"/>
-      <c r="BI5" s="425"/>
-      <c r="BJ5" s="425"/>
-      <c r="BK5" s="425"/>
-      <c r="BL5" s="425"/>
-      <c r="BM5" s="425"/>
-      <c r="BN5" s="425"/>
-      <c r="BO5" s="425"/>
-      <c r="BP5" s="426"/>
-      <c r="BQ5" s="430" t="s">
+      <c r="AZ5" s="413"/>
+      <c r="BA5" s="413"/>
+      <c r="BB5" s="413"/>
+      <c r="BC5" s="413"/>
+      <c r="BD5" s="413"/>
+      <c r="BE5" s="413"/>
+      <c r="BF5" s="413"/>
+      <c r="BG5" s="413"/>
+      <c r="BH5" s="413"/>
+      <c r="BI5" s="413"/>
+      <c r="BJ5" s="413"/>
+      <c r="BK5" s="413"/>
+      <c r="BL5" s="413"/>
+      <c r="BM5" s="413"/>
+      <c r="BN5" s="413"/>
+      <c r="BO5" s="413"/>
+      <c r="BP5" s="414"/>
+      <c r="BQ5" s="433" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="431"/>
-      <c r="BS5" s="424" t="s">
+      <c r="BR5" s="427"/>
+      <c r="BS5" s="412" t="s">
         <v>143</v>
       </c>
-      <c r="BT5" s="424" t="s">
+      <c r="BT5" s="412" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="418" t="s">
+      <c r="BU5" s="444" t="s">
         <v>28</v>
       </c>
-      <c r="BW5" s="421" t="s">
+      <c r="BW5" s="445" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="432" t="s">
+      <c r="BX5" s="434" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="433"/>
-      <c r="BZ5" s="433"/>
-      <c r="CA5" s="431"/>
-      <c r="CB5" s="427" t="s">
+      <c r="BY5" s="435"/>
+      <c r="BZ5" s="435"/>
+      <c r="CA5" s="427"/>
+      <c r="CB5" s="446" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="333" t="s">
+      <c r="CC5" s="362" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="333" t="s">
+      <c r="CD5" s="362" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
     <row r="6" spans="1:87" s="136" customFormat="1">
-      <c r="A6" s="409"/>
-      <c r="B6" s="409"/>
-      <c r="C6" s="409"/>
-      <c r="D6" s="409"/>
-      <c r="E6" s="409"/>
-      <c r="F6" s="409"/>
-      <c r="G6" s="409"/>
-      <c r="H6" s="409"/>
-      <c r="I6" s="409"/>
-      <c r="J6" s="409"/>
-      <c r="K6" s="414" t="s">
+      <c r="A6" s="410"/>
+      <c r="B6" s="410"/>
+      <c r="C6" s="410"/>
+      <c r="D6" s="410"/>
+      <c r="E6" s="410"/>
+      <c r="F6" s="410"/>
+      <c r="G6" s="410"/>
+      <c r="H6" s="410"/>
+      <c r="I6" s="410"/>
+      <c r="J6" s="410"/>
+      <c r="K6" s="425" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="414" t="s">
+      <c r="L6" s="425" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="414" t="s">
+      <c r="M6" s="425" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="414" t="s">
+      <c r="N6" s="425" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="414" t="s">
+      <c r="O6" s="425" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="414" t="s">
+      <c r="P6" s="425" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="414" t="s">
+      <c r="Q6" s="425" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="414" t="s">
+      <c r="R6" s="425" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="414" t="s">
+      <c r="S6" s="425" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="414" t="s">
+      <c r="T6" s="425" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="414" t="s">
+      <c r="U6" s="425" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="445" t="s">
+      <c r="V6" s="426" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="431"/>
-      <c r="X6" s="414" t="s">
+      <c r="W6" s="427"/>
+      <c r="X6" s="425" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="413" t="s">
+      <c r="Y6" s="417" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="413" t="s">
+      <c r="Z6" s="417" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="413" t="s">
+      <c r="AA6" s="417" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="413" t="s">
+      <c r="AB6" s="417" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="417" t="s">
+      <c r="AC6" s="415" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="417" t="s">
+      <c r="AD6" s="415" t="s">
         <v>144</v>
       </c>
-      <c r="AE6" s="417" t="s">
+      <c r="AE6" s="415" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="417" t="s">
+      <c r="AF6" s="415" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="413" t="s">
+      <c r="AG6" s="417" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="417" t="s">
+      <c r="AH6" s="415" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="417" t="s">
+      <c r="AI6" s="415" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="413" t="s">
+      <c r="AJ6" s="417" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="442" t="s">
+      <c r="AK6" s="419" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="413" t="s">
+      <c r="AL6" s="417" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="413" t="s">
+      <c r="AM6" s="417" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="444" t="s">
+      <c r="AN6" s="423" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="413" t="s">
+      <c r="AO6" s="417" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="409"/>
-      <c r="AQ6" s="409"/>
-      <c r="AR6" s="409"/>
-      <c r="AS6" s="409"/>
-      <c r="AT6" s="409"/>
-      <c r="AU6" s="409"/>
-      <c r="AV6" s="409"/>
-      <c r="AW6" s="409"/>
-      <c r="AX6" s="409"/>
-      <c r="AY6" s="424" t="s">
+      <c r="AP6" s="410"/>
+      <c r="AQ6" s="410"/>
+      <c r="AR6" s="410"/>
+      <c r="AS6" s="410"/>
+      <c r="AT6" s="410"/>
+      <c r="AU6" s="410"/>
+      <c r="AV6" s="410"/>
+      <c r="AW6" s="410"/>
+      <c r="AX6" s="410"/>
+      <c r="AY6" s="412" t="s">
         <v>25</v>
       </c>
-      <c r="AZ6" s="425"/>
-      <c r="BA6" s="425"/>
-      <c r="BB6" s="425"/>
-      <c r="BC6" s="425"/>
-      <c r="BD6" s="425"/>
-      <c r="BE6" s="425"/>
-      <c r="BF6" s="425"/>
-      <c r="BG6" s="425"/>
-      <c r="BH6" s="425"/>
-      <c r="BI6" s="425"/>
-      <c r="BJ6" s="426"/>
-      <c r="BK6" s="424" t="s">
+      <c r="AZ6" s="413"/>
+      <c r="BA6" s="413"/>
+      <c r="BB6" s="413"/>
+      <c r="BC6" s="413"/>
+      <c r="BD6" s="413"/>
+      <c r="BE6" s="413"/>
+      <c r="BF6" s="413"/>
+      <c r="BG6" s="413"/>
+      <c r="BH6" s="413"/>
+      <c r="BI6" s="413"/>
+      <c r="BJ6" s="414"/>
+      <c r="BK6" s="412" t="s">
         <v>64</v>
       </c>
-      <c r="BL6" s="425"/>
-      <c r="BM6" s="425"/>
-      <c r="BN6" s="425"/>
-      <c r="BO6" s="425"/>
-      <c r="BP6" s="426"/>
-      <c r="BQ6" s="411" t="s">
+      <c r="BL6" s="413"/>
+      <c r="BM6" s="413"/>
+      <c r="BN6" s="413"/>
+      <c r="BO6" s="413"/>
+      <c r="BP6" s="414"/>
+      <c r="BQ6" s="409" t="s">
         <v>65</v>
       </c>
-      <c r="BR6" s="411" t="s">
+      <c r="BR6" s="409" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="409"/>
-      <c r="BT6" s="409"/>
-      <c r="BU6" s="419"/>
-      <c r="BW6" s="422"/>
-      <c r="BX6" s="419"/>
-      <c r="BY6" s="434"/>
-      <c r="BZ6" s="434"/>
-      <c r="CA6" s="422"/>
-      <c r="CB6" s="409"/>
-      <c r="CC6" s="409"/>
-      <c r="CD6" s="409"/>
+      <c r="BS6" s="410"/>
+      <c r="BT6" s="410"/>
+      <c r="BU6" s="420"/>
+      <c r="BW6" s="437"/>
+      <c r="BX6" s="420"/>
+      <c r="BY6" s="436"/>
+      <c r="BZ6" s="436"/>
+      <c r="CA6" s="437"/>
+      <c r="CB6" s="410"/>
+      <c r="CC6" s="410"/>
+      <c r="CD6" s="410"/>
       <c r="CH6" s="137"/>
       <c r="CI6" s="138"/>
     </row>
     <row r="7" spans="1:87" s="136" customFormat="1" ht="12">
-      <c r="A7" s="409"/>
-      <c r="B7" s="409"/>
-      <c r="C7" s="409"/>
-      <c r="D7" s="409"/>
-      <c r="E7" s="409"/>
-      <c r="F7" s="409"/>
-      <c r="G7" s="409"/>
-      <c r="H7" s="409"/>
-      <c r="I7" s="409"/>
-      <c r="J7" s="409"/>
-      <c r="K7" s="409"/>
-      <c r="L7" s="409"/>
-      <c r="M7" s="409"/>
-      <c r="N7" s="409"/>
-      <c r="O7" s="409"/>
-      <c r="P7" s="409"/>
-      <c r="Q7" s="409"/>
-      <c r="R7" s="409"/>
-      <c r="S7" s="409"/>
-      <c r="T7" s="409"/>
-      <c r="U7" s="409"/>
-      <c r="V7" s="420"/>
-      <c r="W7" s="446"/>
-      <c r="X7" s="409"/>
-      <c r="Y7" s="409"/>
-      <c r="Z7" s="409"/>
-      <c r="AA7" s="409"/>
-      <c r="AB7" s="409"/>
-      <c r="AC7" s="409"/>
-      <c r="AD7" s="409"/>
-      <c r="AE7" s="409"/>
-      <c r="AF7" s="409"/>
-      <c r="AG7" s="409"/>
-      <c r="AH7" s="409"/>
-      <c r="AI7" s="409"/>
-      <c r="AJ7" s="409"/>
-      <c r="AK7" s="419"/>
-      <c r="AL7" s="409"/>
-      <c r="AM7" s="409"/>
-      <c r="AN7" s="409"/>
-      <c r="AO7" s="409"/>
-      <c r="AP7" s="409"/>
-      <c r="AQ7" s="409"/>
-      <c r="AR7" s="409"/>
-      <c r="AS7" s="409"/>
-      <c r="AT7" s="409"/>
-      <c r="AU7" s="409"/>
-      <c r="AV7" s="409"/>
-      <c r="AW7" s="409"/>
-      <c r="AX7" s="409"/>
+      <c r="A7" s="410"/>
+      <c r="B7" s="410"/>
+      <c r="C7" s="410"/>
+      <c r="D7" s="410"/>
+      <c r="E7" s="410"/>
+      <c r="F7" s="410"/>
+      <c r="G7" s="410"/>
+      <c r="H7" s="410"/>
+      <c r="I7" s="410"/>
+      <c r="J7" s="410"/>
+      <c r="K7" s="410"/>
+      <c r="L7" s="410"/>
+      <c r="M7" s="410"/>
+      <c r="N7" s="410"/>
+      <c r="O7" s="410"/>
+      <c r="P7" s="410"/>
+      <c r="Q7" s="410"/>
+      <c r="R7" s="410"/>
+      <c r="S7" s="410"/>
+      <c r="T7" s="410"/>
+      <c r="U7" s="410"/>
+      <c r="V7" s="421"/>
+      <c r="W7" s="428"/>
+      <c r="X7" s="410"/>
+      <c r="Y7" s="410"/>
+      <c r="Z7" s="410"/>
+      <c r="AA7" s="410"/>
+      <c r="AB7" s="410"/>
+      <c r="AC7" s="410"/>
+      <c r="AD7" s="410"/>
+      <c r="AE7" s="410"/>
+      <c r="AF7" s="410"/>
+      <c r="AG7" s="410"/>
+      <c r="AH7" s="410"/>
+      <c r="AI7" s="410"/>
+      <c r="AJ7" s="410"/>
+      <c r="AK7" s="420"/>
+      <c r="AL7" s="410"/>
+      <c r="AM7" s="410"/>
+      <c r="AN7" s="410"/>
+      <c r="AO7" s="410"/>
+      <c r="AP7" s="410"/>
+      <c r="AQ7" s="410"/>
+      <c r="AR7" s="410"/>
+      <c r="AS7" s="410"/>
+      <c r="AT7" s="410"/>
+      <c r="AU7" s="410"/>
+      <c r="AV7" s="410"/>
+      <c r="AW7" s="410"/>
+      <c r="AX7" s="410"/>
       <c r="AY7" s="101" t="s">
         <v>67</v>
       </c>
@@ -19586,122 +19595,122 @@
       <c r="BA7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="BB7" s="424" t="s">
+      <c r="BB7" s="412" t="s">
         <v>70</v>
       </c>
-      <c r="BC7" s="415" t="s">
+      <c r="BC7" s="416" t="s">
         <v>71</v>
       </c>
-      <c r="BD7" s="415" t="s">
+      <c r="BD7" s="416" t="s">
         <v>72</v>
       </c>
-      <c r="BE7" s="415" t="s">
+      <c r="BE7" s="416" t="s">
         <v>145</v>
       </c>
-      <c r="BF7" s="415" t="s">
+      <c r="BF7" s="416" t="s">
         <v>74</v>
       </c>
-      <c r="BG7" s="415" t="s">
+      <c r="BG7" s="416" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" s="415" t="s">
+      <c r="BH7" s="416" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" s="415" t="s">
+      <c r="BI7" s="416" t="s">
         <v>79</v>
       </c>
-      <c r="BJ7" s="416" t="s">
+      <c r="BJ7" s="443" t="s">
         <v>80</v>
       </c>
-      <c r="BK7" s="415" t="s">
+      <c r="BK7" s="416" t="s">
         <v>81</v>
       </c>
-      <c r="BL7" s="424" t="s">
+      <c r="BL7" s="412" t="s">
         <v>82</v>
       </c>
-      <c r="BM7" s="415" t="s">
+      <c r="BM7" s="416" t="s">
         <v>83</v>
       </c>
-      <c r="BN7" s="424" t="s">
+      <c r="BN7" s="412" t="s">
         <v>84</v>
       </c>
-      <c r="BO7" s="424" t="s">
+      <c r="BO7" s="412" t="s">
         <v>146</v>
       </c>
-      <c r="BP7" s="424" t="s">
+      <c r="BP7" s="412" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="409"/>
-      <c r="BR7" s="409"/>
-      <c r="BS7" s="409"/>
-      <c r="BT7" s="409"/>
-      <c r="BU7" s="419"/>
-      <c r="BW7" s="422"/>
-      <c r="BX7" s="435"/>
-      <c r="BY7" s="436"/>
-      <c r="BZ7" s="436"/>
-      <c r="CA7" s="423"/>
-      <c r="CB7" s="409"/>
-      <c r="CC7" s="409"/>
-      <c r="CD7" s="409"/>
+      <c r="BQ7" s="410"/>
+      <c r="BR7" s="410"/>
+      <c r="BS7" s="410"/>
+      <c r="BT7" s="410"/>
+      <c r="BU7" s="420"/>
+      <c r="BW7" s="437"/>
+      <c r="BX7" s="438"/>
+      <c r="BY7" s="439"/>
+      <c r="BZ7" s="439"/>
+      <c r="CA7" s="440"/>
+      <c r="CB7" s="410"/>
+      <c r="CC7" s="410"/>
+      <c r="CD7" s="410"/>
       <c r="CH7" s="137"/>
       <c r="CI7" s="138"/>
     </row>
     <row r="8" spans="1:87" s="136" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A8" s="412"/>
-      <c r="B8" s="412"/>
-      <c r="C8" s="412"/>
-      <c r="D8" s="412"/>
-      <c r="E8" s="412"/>
-      <c r="F8" s="412"/>
-      <c r="G8" s="412"/>
-      <c r="H8" s="412"/>
-      <c r="I8" s="412"/>
-      <c r="J8" s="412"/>
-      <c r="K8" s="412"/>
-      <c r="L8" s="412"/>
-      <c r="M8" s="412"/>
-      <c r="N8" s="412"/>
-      <c r="O8" s="412"/>
-      <c r="P8" s="412"/>
-      <c r="Q8" s="412"/>
-      <c r="R8" s="412"/>
-      <c r="S8" s="412"/>
-      <c r="T8" s="412"/>
-      <c r="U8" s="412"/>
+      <c r="A8" s="411"/>
+      <c r="B8" s="411"/>
+      <c r="C8" s="411"/>
+      <c r="D8" s="411"/>
+      <c r="E8" s="411"/>
+      <c r="F8" s="411"/>
+      <c r="G8" s="411"/>
+      <c r="H8" s="411"/>
+      <c r="I8" s="411"/>
+      <c r="J8" s="411"/>
+      <c r="K8" s="411"/>
+      <c r="L8" s="411"/>
+      <c r="M8" s="411"/>
+      <c r="N8" s="411"/>
+      <c r="O8" s="411"/>
+      <c r="P8" s="411"/>
+      <c r="Q8" s="411"/>
+      <c r="R8" s="411"/>
+      <c r="S8" s="411"/>
+      <c r="T8" s="411"/>
+      <c r="U8" s="411"/>
       <c r="V8" s="140" t="s">
         <v>86</v>
       </c>
       <c r="W8" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="X8" s="412"/>
-      <c r="Y8" s="412"/>
-      <c r="Z8" s="412"/>
-      <c r="AA8" s="412"/>
-      <c r="AB8" s="412"/>
-      <c r="AC8" s="412"/>
-      <c r="AD8" s="412"/>
-      <c r="AE8" s="412"/>
-      <c r="AF8" s="412"/>
-      <c r="AG8" s="412"/>
-      <c r="AH8" s="412"/>
-      <c r="AI8" s="412"/>
-      <c r="AJ8" s="412"/>
-      <c r="AK8" s="420"/>
-      <c r="AL8" s="412"/>
-      <c r="AM8" s="412"/>
-      <c r="AN8" s="412"/>
-      <c r="AO8" s="412"/>
-      <c r="AP8" s="412"/>
-      <c r="AQ8" s="412"/>
-      <c r="AR8" s="412"/>
-      <c r="AS8" s="412"/>
-      <c r="AT8" s="412"/>
-      <c r="AU8" s="412"/>
-      <c r="AV8" s="412"/>
-      <c r="AW8" s="412"/>
-      <c r="AX8" s="412"/>
+      <c r="X8" s="411"/>
+      <c r="Y8" s="411"/>
+      <c r="Z8" s="411"/>
+      <c r="AA8" s="411"/>
+      <c r="AB8" s="411"/>
+      <c r="AC8" s="411"/>
+      <c r="AD8" s="411"/>
+      <c r="AE8" s="411"/>
+      <c r="AF8" s="411"/>
+      <c r="AG8" s="411"/>
+      <c r="AH8" s="411"/>
+      <c r="AI8" s="411"/>
+      <c r="AJ8" s="411"/>
+      <c r="AK8" s="421"/>
+      <c r="AL8" s="411"/>
+      <c r="AM8" s="411"/>
+      <c r="AN8" s="411"/>
+      <c r="AO8" s="411"/>
+      <c r="AP8" s="411"/>
+      <c r="AQ8" s="411"/>
+      <c r="AR8" s="411"/>
+      <c r="AS8" s="411"/>
+      <c r="AT8" s="411"/>
+      <c r="AU8" s="411"/>
+      <c r="AV8" s="411"/>
+      <c r="AW8" s="411"/>
+      <c r="AX8" s="411"/>
       <c r="AY8" s="102" t="s">
         <v>88</v>
       </c>
@@ -19711,27 +19720,27 @@
       <c r="BA8" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="BB8" s="412"/>
-      <c r="BC8" s="412"/>
-      <c r="BD8" s="412"/>
-      <c r="BE8" s="412"/>
-      <c r="BF8" s="412"/>
-      <c r="BG8" s="412"/>
-      <c r="BH8" s="412"/>
-      <c r="BI8" s="412"/>
-      <c r="BJ8" s="412"/>
-      <c r="BK8" s="412"/>
-      <c r="BL8" s="412"/>
-      <c r="BM8" s="412"/>
-      <c r="BN8" s="412"/>
-      <c r="BO8" s="412"/>
-      <c r="BP8" s="412"/>
-      <c r="BQ8" s="412"/>
-      <c r="BR8" s="412"/>
-      <c r="BS8" s="412"/>
-      <c r="BT8" s="412"/>
-      <c r="BU8" s="420"/>
-      <c r="BW8" s="423"/>
+      <c r="BB8" s="411"/>
+      <c r="BC8" s="411"/>
+      <c r="BD8" s="411"/>
+      <c r="BE8" s="411"/>
+      <c r="BF8" s="411"/>
+      <c r="BG8" s="411"/>
+      <c r="BH8" s="411"/>
+      <c r="BI8" s="411"/>
+      <c r="BJ8" s="411"/>
+      <c r="BK8" s="411"/>
+      <c r="BL8" s="411"/>
+      <c r="BM8" s="411"/>
+      <c r="BN8" s="411"/>
+      <c r="BO8" s="411"/>
+      <c r="BP8" s="411"/>
+      <c r="BQ8" s="411"/>
+      <c r="BR8" s="411"/>
+      <c r="BS8" s="411"/>
+      <c r="BT8" s="411"/>
+      <c r="BU8" s="421"/>
+      <c r="BW8" s="440"/>
       <c r="BX8" s="72" t="s">
         <v>91</v>
       </c>
@@ -19744,9 +19753,9 @@
       <c r="CA8" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="CB8" s="410"/>
-      <c r="CC8" s="410"/>
-      <c r="CD8" s="410"/>
+      <c r="CB8" s="432"/>
+      <c r="CC8" s="432"/>
+      <c r="CD8" s="432"/>
       <c r="CF8" s="141"/>
       <c r="CH8" s="137"/>
       <c r="CI8" s="138"/>
@@ -21753,24 +21762,52 @@
   </sheetData>
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="82">
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="D5:D8"/>
     <mergeCell ref="F5:F8"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="AB6:AB8"/>
@@ -21787,54 +21824,26 @@
     <mergeCell ref="AK6:AK8"/>
     <mergeCell ref="AD6:AD8"/>
     <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="K5:X5"/>
     <mergeCell ref="Q6:Q8"/>
     <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="BQ6:BQ8"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="BG7:BG8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 B20:B1048576 C9:BU9 D10:F10 J10:BI10 BK10:BU10 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="6" priority="68"/>
